--- a/docs/支付监控场景_中文版-0709-v2.xlsx
+++ b/docs/支付监控场景_中文版-0709-v2.xlsx
@@ -441,7 +441,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -824,6 +824,24 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4826,9 +4844,11 @@
 4. 在 CPI 和制裁名单里检索对应国家</t>
         </is>
       </c>
-      <c r="N2" s="82" t="inlineStr">
-        <is>
-          <t>Ariba|LGAP|S4 查询客户/供应商/卖方国家、发票国家、银行国家</t>
+      <c r="N2" s="131" t="inlineStr">
+        <is>
+          <t>1. 供应商注册国：S4 供应商主数据（BP，Ariba SLP 入库同步）
+2. 发票开具国：Ariba Network 发票（PO 类）/ LGAP 发票附件（非 PO 类）
+3. 收款银行国：LGVM 维护的银行账户（IBAN/SWIFT 解析），随 S4 付款凭证入账</t>
         </is>
       </c>
       <c r="O2" s="82" t="inlineStr">
@@ -4898,9 +4918,9 @@
 3. 在 FATF 名单里检索对应国家</t>
         </is>
       </c>
-      <c r="N3" s="82" t="inlineStr">
-        <is>
-          <t>Ariba|LGAP|S4 查询付款银行国家</t>
+      <c r="N3" s="131" t="inlineStr">
+        <is>
+          <t>收款银行国：LGVM 银行账户主数据；实际付款/收款银行以 S4 付款凭证（F110）为准</t>
         </is>
       </c>
       <c r="O3" s="82" t="inlineStr">
@@ -4976,9 +4996,10 @@
 3. 在离岸名单中查询运输路径中的国家</t>
         </is>
       </c>
-      <c r="N4" s="82" t="inlineStr">
-        <is>
-          <t>Ariba|LGAP|S4 查询中转路径</t>
+      <c r="N4" s="131" t="inlineStr">
+        <is>
+          <t>起点/终点：Ariba PO 的 ship-from / ship-to + S4 交货单（GR）
+⚠️ 完整中转路径不在采购/财务系统 —— 需对接物流 TMS/货代数据（待 DT 确认）</t>
         </is>
       </c>
       <c r="O4" s="82" t="inlineStr">
@@ -5048,10 +5069,10 @@
 在联想内部查询上述对手方已知曾参与腐败活动方的付款记录</t>
         </is>
       </c>
-      <c r="N5" s="82" t="inlineStr">
-        <is>
-          <t>1. Ariba|LGAP|S4 查询客户/供应商/卖方
-2. 在联想内部查询上述对手方已知曾参与腐败活动方的付款记录</t>
+      <c r="N5" s="131" t="inlineStr">
+        <is>
+          <t>1. 供应商名单：S4 供应商主数据（BP）
+2. 腐败关联方付款记录：S4 应付账款历史（AP 凭证按供应商汇总）</t>
         </is>
       </c>
       <c r="O5" s="88" t="inlineStr">
@@ -5122,9 +5143,9 @@
     b：上述人物是否在 PEP 数据中</t>
         </is>
       </c>
-      <c r="N6" s="82" t="inlineStr">
-        <is>
-          <t>Ariba|LGAP|S4 查询客户/供应商/卖方</t>
+      <c r="N6" s="131" t="inlineStr">
+        <is>
+          <t>供应商名称与注册信息：S4 供应商主数据（BP，Ariba SLP 入库同步）</t>
         </is>
       </c>
       <c r="O6" s="88" t="inlineStr">
@@ -5199,9 +5220,9 @@
 2. AI 筛查工具（LLM）结合天眼查或 DJ 数据识别主要经营地和收款国家进行匹配</t>
         </is>
       </c>
-      <c r="N7" s="82" t="inlineStr">
-        <is>
-          <t>Ariba|LGAP|S4 查询供应商收款银行国家</t>
+      <c r="N7" s="131" t="inlineStr">
+        <is>
+          <t>收款银行国：LGVM 银行账户（IBAN/SWIFT 前缀解析）；实际付款银行以 S4 付款凭证为准</t>
         </is>
       </c>
       <c r="O7" s="88" t="inlineStr">
@@ -5275,10 +5296,10 @@
 2. 核对发票上银行国家与供应商国家</t>
         </is>
       </c>
-      <c r="N8" s="82" t="inlineStr">
-        <is>
-          <t>1. Ariba|LGAP|S4 查询付款方国家
-2. Ariba|LGAP|S4 查询发票开具地信息</t>
+      <c r="N8" s="131" t="inlineStr">
+        <is>
+          <t>1. 付款方国家：S4 公司代码（company code）所属国
+2. 发票开具地：Ariba Network 发票抬头（PO 类）/ LGAP 发票附件（非 PO 类，可能需 OCR）</t>
         </is>
       </c>
       <c r="O8" s="79" t="inlineStr">
@@ -5345,7 +5366,11 @@
           <t>1. 确认此情况仅发生在 LGAP，属正常场景</t>
         </is>
       </c>
-      <c r="N9" s="94" t="n"/>
+      <c r="N9" s="132" t="inlineStr">
+        <is>
+          <t>LGAP 付款申请记录（无 PO 场景仅存在于 LGAP）</t>
+        </is>
+      </c>
       <c r="O9" s="94" t="n"/>
     </row>
     <row r="10" ht="126" customHeight="1" s="63">
@@ -5405,9 +5430,10 @@
 4. 客户/供应商/卖方的经营范围和 PO 内容进行相关性计算，是否符合</t>
         </is>
       </c>
-      <c r="N10" s="82" t="inlineStr">
-        <is>
-          <t>Ariba|LGAP|S4 查询客户/供应商/卖方</t>
+      <c r="N10" s="131" t="inlineStr">
+        <is>
+          <t>1. 供应商信息：S4 供应商主数据
+2. 历史 PO 金额：Ariba PO 历史（非 PO 渠道用 LGAP 付款申请历史汇总）</t>
         </is>
       </c>
       <c r="O10" s="88" t="inlineStr">
@@ -5478,9 +5504,10 @@
 2. AI 筛查工具（LLM）结合天眼查或 DJ 数据</t>
         </is>
       </c>
-      <c r="N11" s="82" t="inlineStr">
-        <is>
-          <t>Ariba|LGAP|S4 查询客户/供应商/卖方 PO 的品类</t>
+      <c r="N11" s="131" t="inlineStr">
+        <is>
+          <t>PO 品类：Ariba PO commodity code（UNSPSC 品类树）；辅：S4 采购订单物料组
+⚠️ LGAP 渠道无 PO 品类 —— 需用费用类别/总账科目替代</t>
         </is>
       </c>
       <c r="O11" s="88" t="inlineStr">
@@ -5547,9 +5574,10 @@
 突增：付款增长 500%。</t>
         </is>
       </c>
-      <c r="N12" s="82" t="inlineStr">
-        <is>
-          <t>获取新供应商历史订单信息</t>
+      <c r="N12" s="131" t="inlineStr">
+        <is>
+          <t>1. 供应商入库日期：S4 供应商主数据 / Ariba SLP
+2. 历史付款流水：S4 付款凭证（全渠道汇总，含 LGAP 通道付款）</t>
         </is>
       </c>
       <c r="O12" s="94" t="n"/>
@@ -5608,9 +5636,10 @@
 2. 用开放工具核对付款日期是否是所在国家的公共节假日</t>
         </is>
       </c>
-      <c r="N13" s="88" t="inlineStr">
-        <is>
-          <t>从 PO 查询付款数据（日期、国家）</t>
+      <c r="N13" s="133" t="inlineStr">
+        <is>
+          <t>付款日期：S4 付款凭证的实际执行/清账日期（勿用 Ariba/LGAP 的申请日）
+付款国家：S4 公司代码所属国 + 收款银行国</t>
         </is>
       </c>
       <c r="O13" s="101" t="inlineStr">
@@ -5670,9 +5699,11 @@
 2. AI 筛查工具（LLM）结合天眼查或 DJ 数据上，客户和收款帐户之间的联系（是否关联公司）</t>
         </is>
       </c>
-      <c r="N14" s="82" t="inlineStr">
-        <is>
-          <t>从 Ariba|LGAP|S4 查询客户/供应商/卖方</t>
+      <c r="N14" s="131" t="inlineStr">
+        <is>
+          <t>1. 供应商登记账户：LGVM 银行账户主数据（含变更历史）
+2. 实际收款账户：S4/LGAP 付款请求中的收款账户
+3. 比对两者是否一致</t>
         </is>
       </c>
       <c r="O14" s="88" t="inlineStr">
@@ -5733,7 +5764,12 @@
       </c>
       <c r="L15" s="108" t="n"/>
       <c r="M15" s="79" t="n"/>
-      <c r="N15" s="82" t="n"/>
+      <c r="N15" s="131" t="inlineStr">
+        <is>
+          <t>发票原件/影像：Ariba Network（PO 类）/ LGAP 附件（非 PO 类）
+历史发票号库：S4 AP 凭证</t>
+        </is>
+      </c>
       <c r="O15" s="79" t="n"/>
       <c r="P15" s="86" t="inlineStr">
         <is>
@@ -5853,10 +5889,6 @@
       <c r="F21" s="89" t="n"/>
       <c r="G21" s="87" t="n"/>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26" ht="198" customFormat="1" customHeight="1" s="118">
       <c r="A26" s="71" t="inlineStr">
         <is>
@@ -5875,19 +5907,13 @@
       <c r="K26" s="77" t="n"/>
       <c r="L26" s="77" t="n"/>
       <c r="M26" s="77" t="n"/>
-      <c r="N26" s="79" t="inlineStr">
-        <is>
-          <t>Ariba | LGAP | S4 查询：
-客户：
-    a. 客户/供应商/卖方信息，所在国家
-付款：
-    b. 付款国家
-    c. 付款日期
-发票：
-    d. 发票信息：付款方信息国家、发票开具地信息
-订单：
-    e. 订单的运输完整路径
-    f. PO 品类</t>
+      <c r="N26" s="134" t="inlineStr">
+        <is>
+          <t>【S4 · 财务核心（记账真源）】
+a. 供应商主数据（BP，Ariba SLP 同步）：名称、注册国、地址
+b. 付款凭证（F110）：实际付款日期、金额、币种、收款银行
+c. 公司代码主数据：付款方国家
+d. 应付账款（AP）历史：按供应商汇总的付款记录（腐败关联回溯、突增基线）</t>
         </is>
       </c>
       <c r="O26" s="79" t="inlineStr">
@@ -5918,9 +5944,12 @@
       <c r="K27" s="120" t="n"/>
       <c r="L27" s="120" t="n"/>
       <c r="M27" s="120" t="n"/>
-      <c r="N27" s="123" t="inlineStr">
-        <is>
-          <t>在联想内部查询上述对手方已知曾参与腐败活动方的付款记录</t>
+      <c r="N27" s="135" t="inlineStr">
+        <is>
+          <t>【Ariba · 采购前端】
+e. SLP 供应商入库：注册信息、入库日期
+f. PO：品类（commodity code）、ship-from/ship-to、金额、历史 PO 列表
+g. Ariba Network 发票：开票方、开票地、发票号、金额</t>
         </is>
       </c>
       <c r="O27" s="124" t="inlineStr">
@@ -5943,9 +5972,11 @@
       <c r="K28" s="120" t="n"/>
       <c r="L28" s="120" t="n"/>
       <c r="M28" s="120" t="n"/>
-      <c r="N28" s="124" t="inlineStr">
-        <is>
-          <t>PO 历史记录列表，查询客户/供应商/卖方信息采购项目</t>
+      <c r="N28" s="134" t="inlineStr">
+        <is>
+          <t>【LGAP · 非 PO 付款通道】
+h. 付款申请：申请日、费用类别、收款账户、金额
+i. 发票附件（结构化程度待 DT 确认，可能需 OCR）</t>
         </is>
       </c>
       <c r="O28" s="123" t="inlineStr">
@@ -5968,7 +5999,13 @@
       <c r="K29" s="120" t="n"/>
       <c r="L29" s="120" t="n"/>
       <c r="M29" s="120" t="n"/>
-      <c r="N29" s="124" t="n"/>
+      <c r="N29" s="131" t="inlineStr">
+        <is>
+          <t>【LGVM · 供应商银行账户】
+j. 收款银行账户主数据（IBAN/SWIFT → 银行国别）
+k. 账户变更历史（支持"收款账户频繁变更"指标）</t>
+        </is>
+      </c>
       <c r="O29" s="82" t="inlineStr">
         <is>
           <t>FATF 黑/灰名单（FATF，https://www.fatf-gafi.org/en/countries/black-and-grey-lists.html）</t>
@@ -5989,18 +6026,19 @@
       <c r="K30" s="120" t="n"/>
       <c r="L30" s="120" t="n"/>
       <c r="M30" s="120" t="n"/>
-      <c r="N30" s="124" t="n"/>
+      <c r="N30" s="131" t="inlineStr">
+        <is>
+          <t>【缺口 · 三系统之外】
+l. 订单完整运输路径 → 物流 TMS/货代系统（待 DT 确认）
+m. 实际经营地/股权/诉讼/PEP → 外部数据（天眼查/DJ，见右列）</t>
+        </is>
+      </c>
       <c r="O30" s="82" t="inlineStr">
         <is>
           <t>离岸名单（https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Glossary:List_of_offshore_financial_centres）</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36">
       <c r="N36" s="84" t="inlineStr">
         <is>
@@ -6023,9 +6061,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="N39" s="84" t="inlineStr">
-        <is>
-          <t>客户/供应商/卖方信息在哪个系统？</t>
+      <c r="N39" s="136" t="inlineStr">
+        <is>
+          <t>客户/供应商/卖方信息在哪个系统？
+→ 主数据：S4（BP）；入库注册：Ariba SLP；银行账户：LGVM</t>
         </is>
       </c>
     </row>
@@ -6219,9 +6258,11 @@
 4. Look up the countries in the CPI and sanctions lists</t>
         </is>
       </c>
-      <c r="N2" s="82" t="inlineStr">
-        <is>
-          <t>Query customer/supplier/vendor country, invoice country, bank country from Ariba|LGAP|S4</t>
+      <c r="N2" s="131" t="inlineStr">
+        <is>
+          <t>1. Vendor registration country: S4 vendor master (BP, synced from Ariba SLP onboarding)
+2. Invoice-issuing country: Ariba Network invoice (PO flow) / LGAP invoice attachment (non-PO flow)
+3. Receiving-bank country: bank account maintained in LGVM (parsed from IBAN/SWIFT), posted with the S4 payment document</t>
         </is>
       </c>
       <c r="O2" s="82" t="inlineStr">
@@ -6291,9 +6332,9 @@
 3. Look up the countries in the FATF list</t>
         </is>
       </c>
-      <c r="N3" s="82" t="inlineStr">
-        <is>
-          <t>Query paying bank country from Ariba|LGAP|S4</t>
+      <c r="N3" s="131" t="inlineStr">
+        <is>
+          <t>Receiving-bank country: LGVM bank-account master data; actual paying/receiving bank per the S4 payment document (F110)</t>
         </is>
       </c>
       <c r="O3" s="82" t="inlineStr">
@@ -6369,9 +6410,10 @@
 3. Look up the countries along the route in the offshore list</t>
         </is>
       </c>
-      <c r="N4" s="82" t="inlineStr">
-        <is>
-          <t>Query the transit route from Ariba|LGAP|S4</t>
+      <c r="N4" s="131" t="inlineStr">
+        <is>
+          <t>Origin/destination: ship-from / ship-to on the Ariba PO + S4 delivery documents (GR)
+⚠️ The full transit route is not in procurement/finance systems — needs logistics TMS / forwarder data (confirm with DT)</t>
         </is>
       </c>
       <c r="O4" s="82" t="inlineStr">
@@ -6441,10 +6483,10 @@
 Search Lenovo internal records for payments to the above counterparties known to have been involved in corrupt activities</t>
         </is>
       </c>
-      <c r="N5" s="82" t="inlineStr">
-        <is>
-          <t>1. Query customers/suppliers/vendors from Ariba|LGAP|S4
-2. Search Lenovo internal records for payments to counterparties known to have been involved in corrupt activities</t>
+      <c r="N5" s="131" t="inlineStr">
+        <is>
+          <t>1. Vendor list: S4 vendor master (BP)
+2. Payments to corruption-linked parties: S4 AP history (AP documents aggregated by vendor)</t>
         </is>
       </c>
       <c r="O5" s="88" t="inlineStr">
@@ -6515,9 +6557,9 @@
     b: whether the above individuals appear in PEP data</t>
         </is>
       </c>
-      <c r="N6" s="82" t="inlineStr">
-        <is>
-          <t>Query customers/suppliers/vendors from Ariba|LGAP|S4</t>
+      <c r="N6" s="131" t="inlineStr">
+        <is>
+          <t>Vendor name and registration info: S4 vendor master (BP, synced from Ariba SLP onboarding)</t>
         </is>
       </c>
       <c r="O6" s="88" t="inlineStr">
@@ -6592,9 +6634,9 @@
 2. AI screening tool (LLM) with Tianyancha or DJ data to identify the principal place of business and match it against the receiving country</t>
         </is>
       </c>
-      <c r="N7" s="82" t="inlineStr">
-        <is>
-          <t>Query supplier receiving-bank country from Ariba|LGAP|S4</t>
+      <c r="N7" s="131" t="inlineStr">
+        <is>
+          <t>Receiving-bank country: LGVM bank account (parsed from IBAN/SWIFT prefix); actual paying bank per the S4 payment document</t>
         </is>
       </c>
       <c r="O7" s="88" t="inlineStr">
@@ -6668,10 +6710,10 @@
 2. Match bank country on the invoice with supplier country</t>
         </is>
       </c>
-      <c r="N8" s="82" t="inlineStr">
-        <is>
-          <t>1. Query payer country from Ariba|LGAP|S4
-2. Query invoice origin from Ariba|LGAP|S4</t>
+      <c r="N8" s="131" t="inlineStr">
+        <is>
+          <t>1. Payer country: country of the S4 company code
+2. Invoice origin: Ariba Network invoice header (PO flow) / LGAP invoice attachment (non-PO flow, may need OCR)</t>
         </is>
       </c>
       <c r="O8" s="79" t="inlineStr">
@@ -6738,7 +6780,11 @@
           <t>1. Confirm this only happens in LGAP — normal scenario</t>
         </is>
       </c>
-      <c r="N9" s="94" t="n"/>
+      <c r="N9" s="132" t="inlineStr">
+        <is>
+          <t>LGAP payment-request records (the no-PO scenario exists only in LGAP)</t>
+        </is>
+      </c>
       <c r="O9" s="94" t="n"/>
     </row>
     <row r="10" ht="126" customHeight="1" s="63">
@@ -6798,9 +6844,10 @@
 4. Compute relevance between the counterparty's business scope and the PO content — do they match</t>
         </is>
       </c>
-      <c r="N10" s="82" t="inlineStr">
-        <is>
-          <t>Query customers/suppliers/vendors from Ariba|LGAP|S4</t>
+      <c r="N10" s="131" t="inlineStr">
+        <is>
+          <t>1. Vendor info: S4 vendor master
+2. Historical PO amounts: Ariba PO history (for the non-PO channel, aggregate LGAP payment-request history)</t>
         </is>
       </c>
       <c r="O10" s="88" t="inlineStr">
@@ -6871,9 +6918,10 @@
 2. AI screening tool (LLM) with Tianyancha or DJ data</t>
         </is>
       </c>
-      <c r="N11" s="82" t="inlineStr">
-        <is>
-          <t>Query the customer/supplier/vendor PO category from Ariba|LGAP|S4</t>
+      <c r="N11" s="131" t="inlineStr">
+        <is>
+          <t>PO category: Ariba PO commodity code (UNSPSC taxonomy); fallback: S4 purchase-order material group
+⚠️ The LGAP channel has no PO category — use expense type / GL account instead</t>
         </is>
       </c>
       <c r="O11" s="88" t="inlineStr">
@@ -6940,9 +6988,10 @@
 Sudden surge: 500% payment increase.</t>
         </is>
       </c>
-      <c r="N12" s="82" t="inlineStr">
-        <is>
-          <t>Get the new vendor's historical order data</t>
+      <c r="N12" s="131" t="inlineStr">
+        <is>
+          <t>1. Vendor onboarding date: S4 vendor master / Ariba SLP
+2. Historical payment records: S4 payment documents (aggregated across all channels, incl. LGAP payments)</t>
         </is>
       </c>
       <c r="O12" s="94" t="n"/>
@@ -7001,9 +7050,10 @@
 2. Use open tools to check whether the payment date is a public holiday in that country</t>
         </is>
       </c>
-      <c r="N13" s="88" t="inlineStr">
-        <is>
-          <t>Query payment data (date, country) from the PO</t>
+      <c r="N13" s="133" t="inlineStr">
+        <is>
+          <t>Payment date: actual execution/clearing date on the S4 payment document (do NOT use Ariba/LGAP request dates)
+Payment country: S4 company-code country + receiving-bank country</t>
         </is>
       </c>
       <c r="O13" s="101" t="inlineStr">
@@ -7063,9 +7113,11 @@
 2. AI screening tool (LLM) with Tianyancha or DJ data on the link between the counterparty and the receiving account (affiliated company or not)</t>
         </is>
       </c>
-      <c r="N14" s="82" t="inlineStr">
-        <is>
-          <t>Query customers/suppliers/vendors from Ariba|LGAP|S4</t>
+      <c r="N14" s="131" t="inlineStr">
+        <is>
+          <t>1. Registered vendor account: LGVM bank-account master (incl. change history)
+2. Actual receiving account: receiving account on the S4/LGAP payment request
+3. Compare the two for consistency</t>
         </is>
       </c>
       <c r="O14" s="88" t="inlineStr">
@@ -7126,7 +7178,12 @@
       </c>
       <c r="L15" s="108" t="n"/>
       <c r="M15" s="79" t="n"/>
-      <c r="N15" s="82" t="n"/>
+      <c r="N15" s="131" t="inlineStr">
+        <is>
+          <t>Invoice originals/images: Ariba Network (PO flow) / LGAP attachments (non-PO flow)
+Historical invoice-number library: S4 AP documents</t>
+        </is>
+      </c>
       <c r="O15" s="79" t="n"/>
       <c r="P15" s="86" t="inlineStr">
         <is>
@@ -7246,10 +7303,6 @@
       <c r="F21" s="89" t="n"/>
       <c r="G21" s="87" t="n"/>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26" ht="198" customHeight="1" s="63">
       <c r="A26" s="71" t="inlineStr">
         <is>
@@ -7268,19 +7321,13 @@
       <c r="K26" s="77" t="n"/>
       <c r="L26" s="77" t="n"/>
       <c r="M26" s="77" t="n"/>
-      <c r="N26" s="79" t="inlineStr">
-        <is>
-          <t>Query from Ariba | LGAP | S4:
-Customer:
-    a. Customer/supplier/vendor info, country
-Payment:
-    b. Payment country
-    c. Payment date
-Invoice:
-    d. Invoice info: payer country, invoice origin
-Order:
-    e. Full shipping route of the order
-    f. PO category</t>
+      <c r="N26" s="134" t="inlineStr">
+        <is>
+          <t>[S4 · Finance core (system of record)]
+a. Vendor master (BP, synced from Ariba SLP): name, registration country, address
+b. Payment documents (F110): actual payment date, amount, currency, receiving bank
+c. Company-code master: payer country
+d. AP history: payment records aggregated by vendor (corruption-link lookback, surge baseline)</t>
         </is>
       </c>
       <c r="O26" s="79" t="inlineStr">
@@ -7311,9 +7358,12 @@
       <c r="K27" s="120" t="n"/>
       <c r="L27" s="120" t="n"/>
       <c r="M27" s="120" t="n"/>
-      <c r="N27" s="123" t="inlineStr">
-        <is>
-          <t>Search Lenovo internal records for payments to counterparties known to have been involved in corrupt activities</t>
+      <c r="N27" s="135" t="inlineStr">
+        <is>
+          <t>[Ariba · Procurement front end]
+e. SLP vendor onboarding: registration info, onboarding date
+f. PO: category (commodity code), ship-from/ship-to, amount, PO history list
+g. Ariba Network invoices: issuer, issuing location, invoice number, amount</t>
         </is>
       </c>
       <c r="O27" s="124" t="inlineStr">
@@ -7336,9 +7386,11 @@
       <c r="K28" s="120" t="n"/>
       <c r="L28" s="120" t="n"/>
       <c r="M28" s="120" t="n"/>
-      <c r="N28" s="124" t="inlineStr">
-        <is>
-          <t>PO history list; query customer/supplier/vendor procurement projects</t>
+      <c r="N28" s="134" t="inlineStr">
+        <is>
+          <t>[LGAP · Non-PO payment channel]
+h. Payment requests: request date, expense type, receiving account, amount
+i. Invoice attachments (structure level to be confirmed with DT; may need OCR)</t>
         </is>
       </c>
       <c r="O28" s="123" t="inlineStr">
@@ -7361,7 +7413,13 @@
       <c r="K29" s="120" t="n"/>
       <c r="L29" s="120" t="n"/>
       <c r="M29" s="120" t="n"/>
-      <c r="N29" s="124" t="n"/>
+      <c r="N29" s="131" t="inlineStr">
+        <is>
+          <t>[LGVM · Vendor bank accounts]
+j. Receiving bank-account master (IBAN/SWIFT → bank country)
+k. Account change history (supports the 'receiving-account churn' indicator)</t>
+        </is>
+      </c>
       <c r="O29" s="82" t="inlineStr">
         <is>
           <t>FATF Black/Grey List (FATF, https://www.fatf-gafi.org/en/countries/black-and-grey-lists.html)</t>
@@ -7382,18 +7440,19 @@
       <c r="K30" s="120" t="n"/>
       <c r="L30" s="120" t="n"/>
       <c r="M30" s="120" t="n"/>
-      <c r="N30" s="124" t="n"/>
+      <c r="N30" s="131" t="inlineStr">
+        <is>
+          <t>[Gaps · Outside the three systems]
+l. Full shipping route of orders → logistics TMS / forwarder systems (confirm with DT)
+m. Actual place of business / ownership / litigation / PEP → external data (Tianyancha/DJ, see the right column)</t>
+        </is>
+      </c>
       <c r="O30" s="82" t="inlineStr">
         <is>
           <t>Offshore list (https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Glossary:List_of_offshore_financial_centres)</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36">
       <c r="N36" s="84" t="inlineStr">
         <is>
@@ -7416,9 +7475,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="N39" s="84" t="inlineStr">
-        <is>
-          <t>Which system holds customer/supplier/vendor info?</t>
+      <c r="N39" s="136" t="inlineStr">
+        <is>
+          <t>Which system holds customer/supplier/vendor info?
+→ Master data: S4 (BP); onboarding: Ariba SLP; bank accounts: LGVM</t>
         </is>
       </c>
     </row>

--- a/docs/支付监控场景_中文版-0709-v2.xlsx
+++ b/docs/支付监控场景_中文版-0709-v2.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -214,6 +214,10 @@
       <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="11">
@@ -441,7 +445,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -841,6 +845,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1205,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="4" min="1" max="1"/>
@@ -1220,6 +1230,7 @@
     <col width="28.6640625" customWidth="1" style="4" min="11" max="11"/>
     <col width="8.1640625" customWidth="1" style="4" min="12" max="12"/>
     <col width="8.1640625" customWidth="1" style="4" min="13" max="16384"/>
+    <col width="18" customWidth="1" style="63" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="63">
@@ -1288,6 +1299,11 @@
           <t>数据来源</t>
         </is>
       </c>
+      <c r="N1" s="137" t="inlineStr">
+        <is>
+          <t>适用方向</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1" ht="80" customHeight="1" s="63">
       <c r="A2" s="9" t="inlineStr">
@@ -1346,6 +1362,11 @@
           <t>外部数据库</t>
         </is>
       </c>
+      <c r="N2" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="3" hidden="1" ht="48" customHeight="1" s="63">
       <c r="A3" s="9" t="inlineStr">
@@ -1400,6 +1421,11 @@
           <t>外部数据库</t>
         </is>
       </c>
+      <c r="N3" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="4" hidden="1" ht="48" customHeight="1" s="63">
       <c r="A4" s="9" t="inlineStr">
@@ -1459,6 +1485,11 @@
           <t>避税天堂名单</t>
         </is>
       </c>
+      <c r="N4" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="5" hidden="1" ht="64" customHeight="1" s="63">
       <c r="A5" s="9" t="inlineStr">
@@ -1513,6 +1544,11 @@
           <t>AI 筛查工具</t>
         </is>
       </c>
+      <c r="N5" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="6" hidden="1" ht="102" customHeight="1" s="63">
       <c r="A6" s="9" t="inlineStr">
@@ -1567,6 +1603,11 @@
           <t>AI 筛查工具</t>
         </is>
       </c>
+      <c r="N6" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="7" hidden="1" ht="96" customHeight="1" s="63">
       <c r="A7" s="9" t="inlineStr">
@@ -1623,6 +1664,11 @@
           <t>外部数据库</t>
         </is>
       </c>
+      <c r="N7" s="138" t="inlineStr">
+        <is>
+          <t>双向（当前仅实施采购侧）</t>
+        </is>
+      </c>
     </row>
     <row r="8" hidden="1" ht="96" customHeight="1" s="63">
       <c r="A8" s="13" t="inlineStr">
@@ -1684,6 +1730,11 @@
           <t>company code（公司代码）；ship from（发货地）；Remit To Address（汇款地址）；contract region（合同区域）</t>
         </is>
       </c>
+      <c r="N8" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="29.25" customHeight="1" s="63">
       <c r="A9" s="13" t="inlineStr">
@@ -1731,6 +1782,11 @@
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>编码：仅发生在 LGAP，属正常场景</t>
+        </is>
+      </c>
+      <c r="N9" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
         </is>
       </c>
     </row>
@@ -1785,6 +1841,11 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="N10" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="11" hidden="1" ht="80" customHeight="1" s="63">
       <c r="A11" s="9" t="inlineStr">
@@ -1837,6 +1898,11 @@
       <c r="K11" s="4" t="inlineStr">
         <is>
           <t>ML</t>
+        </is>
+      </c>
+      <c r="N11" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
         </is>
       </c>
     </row>
@@ -1892,6 +1958,11 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="N12" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="96" customHeight="1" s="63">
       <c r="A13" s="13" t="inlineStr">
@@ -1948,6 +2019,11 @@
           <t>以付款方所在地的周末或节假日为准。</t>
         </is>
       </c>
+      <c r="N13" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="112" customHeight="1" s="63">
       <c r="A14" s="9" t="inlineStr">
@@ -1995,6 +2071,11 @@
         </is>
       </c>
       <c r="J14" s="11" t="n"/>
+      <c r="N14" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="15" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="25">
       <c r="A15" s="26" t="inlineStr">
@@ -2041,6 +2122,11 @@
         </is>
       </c>
       <c r="J15" s="24" t="n"/>
+      <c r="N15" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="112" customFormat="1" customHeight="1" s="20">
       <c r="A16" s="21" t="inlineStr">
@@ -2097,6 +2183,11 @@
           <t>ML：趋势监控</t>
         </is>
       </c>
+      <c r="N16" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="48" customFormat="1" customHeight="1" s="20">
       <c r="A17" s="21" t="inlineStr">
@@ -2151,6 +2242,11 @@
           <t>ML：趋势监控</t>
         </is>
       </c>
+      <c r="N17" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="64" customFormat="1" customHeight="1" s="20">
       <c r="A18" s="16" t="inlineStr">
@@ -2201,6 +2297,11 @@
           <t>？</t>
         </is>
       </c>
+      <c r="N18" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="19" hidden="1" ht="32" customFormat="1" customHeight="1" s="20">
       <c r="A19" s="16" t="inlineStr">
@@ -2251,6 +2352,11 @@
           <t>ML？可能超出范围，因为 Ariba 不维护银行账户，归 LGVM 管</t>
         </is>
       </c>
+      <c r="N19" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="20" hidden="1" ht="48" customFormat="1" customHeight="1" s="20">
       <c r="A20" s="16" t="inlineStr">
@@ -2301,6 +2407,11 @@
           <t>ML？可能超出范围，因为 Ariba 不维护银行账户，归 LGVM 管</t>
         </is>
       </c>
+      <c r="N20" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="32" customFormat="1" customHeight="1" s="20">
       <c r="A21" s="16" t="inlineStr">
@@ -2349,6 +2460,11 @@
       <c r="K21" s="20" t="inlineStr">
         <is>
           <t>编码：仅发生在 LGAP</t>
+        </is>
+      </c>
+      <c r="N21" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
         </is>
       </c>
     </row>
@@ -2402,6 +2518,11 @@
           <t>ML：趋势监控</t>
         </is>
       </c>
+      <c r="N22" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="32" customFormat="1" customHeight="1" s="20">
       <c r="A23" s="16" t="inlineStr">
@@ -2453,6 +2574,11 @@
           <t>ML：趋势监控</t>
         </is>
       </c>
+      <c r="N23" s="138" t="inlineStr">
+        <is>
+          <t>双向（当前仅实施采购侧）</t>
+        </is>
+      </c>
     </row>
     <row r="24" hidden="1" ht="16" customFormat="1" customHeight="1" s="20">
       <c r="A24" s="16" t="inlineStr">
@@ -2502,6 +2628,11 @@
           <t>内部数据库</t>
         </is>
       </c>
+      <c r="N24" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="25" hidden="1" ht="102" customFormat="1" customHeight="1" s="20">
       <c r="A25" s="16" t="inlineStr">
@@ -2552,6 +2683,11 @@
           <t>AI 筛查工具</t>
         </is>
       </c>
+      <c r="N25" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="16" customFormat="1" customHeight="1" s="20">
       <c r="A26" s="16" t="inlineStr">
@@ -2601,6 +2737,11 @@
           <t>ML：趋势监控</t>
         </is>
       </c>
+      <c r="N26" s="138" t="inlineStr">
+        <is>
+          <t>客户侧（当前范围外）</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="16" customFormat="1" customHeight="1" s="20">
       <c r="A27" s="21" t="inlineStr">
@@ -2650,6 +2791,11 @@
           <t>外部数据库</t>
         </is>
       </c>
+      <c r="N27" s="138" t="inlineStr">
+        <is>
+          <t>客户侧（当前范围外）</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="16" customFormat="1" customHeight="1" s="20">
       <c r="A28" s="21" t="inlineStr">
@@ -2703,6 +2849,11 @@
           <t>ML：趋势监控</t>
         </is>
       </c>
+      <c r="N28" s="138" t="inlineStr">
+        <is>
+          <t>客户侧（采购侧已禁现金）</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="17" customFormat="1" customHeight="1" s="20">
       <c r="A29" s="21" t="inlineStr">
@@ -2750,6 +2901,11 @@
       <c r="K29" s="20" t="inlineStr">
         <is>
           <t>阈值</t>
+        </is>
+      </c>
+      <c r="N29" s="138" t="inlineStr">
+        <is>
+          <t>双向（原文偏客户侧，DT 按采购侧理解）</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4850,7 @@
     <col width="39.6640625" customWidth="1" style="84" min="13" max="13"/>
     <col width="41.6640625" customWidth="1" style="84" min="14" max="15"/>
     <col hidden="1" width="26.83203125" customWidth="1" style="84" min="16" max="16"/>
-    <col width="8.83203125" customWidth="1" style="112" min="17" max="16384"/>
+    <col width="18" customWidth="1" style="112" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="63">
@@ -4778,6 +4934,11 @@
           <t>问题</t>
         </is>
       </c>
+      <c r="Q1" s="74" t="inlineStr">
+        <is>
+          <t>适用方向</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="96" customHeight="1" s="63">
       <c r="B2" s="77" t="inlineStr">
@@ -4857,6 +5018,11 @@
 制裁名单（）</t>
         </is>
       </c>
+      <c r="Q2" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1" s="63">
       <c r="B3" s="77" t="inlineStr">
@@ -4934,7 +5100,11 @@
 Basel AML 指数</t>
         </is>
       </c>
-      <c r="Q3" s="87" t="n"/>
+      <c r="Q3" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="64" customHeight="1" s="63">
       <c r="B4" s="77" t="inlineStr">
@@ -5005,6 +5175,11 @@
       <c r="O4" s="82" t="inlineStr">
         <is>
           <t>离岸名单（https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Glossary:List_of_offshore_financial_centres）</t>
+        </is>
+      </c>
+      <c r="Q4" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
         </is>
       </c>
     </row>
@@ -5078,6 +5253,11 @@
       <c r="O5" s="88" t="inlineStr">
         <is>
           <t>中国用天眼查，其他地区用 Dow Jones 查询诉讼</t>
+        </is>
+      </c>
+      <c r="Q5" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
         </is>
       </c>
     </row>
@@ -5153,6 +5333,11 @@
           <t>中国用天眼查，其他地区用 Dow Jones</t>
         </is>
       </c>
+      <c r="Q6" s="138" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1" s="63">
       <c r="A7" s="89" t="inlineStr">
@@ -5230,6 +5415,11 @@
           <t>中国用天眼查，其他地区用 Dow Jones 查询公司主要经营地</t>
         </is>
       </c>
+      <c r="Q7" s="138" t="inlineStr">
+        <is>
+          <t>双向（当前仅实施采购侧）</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1" s="63">
       <c r="A8" s="89" t="inlineStr">
@@ -5310,6 +5500,11 @@
       <c r="P8" s="92" t="inlineStr">
         <is>
           <t>与第 7 条的区别是什么？</t>
+        </is>
+      </c>
+      <c r="Q8" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
         </is>
       </c>
     </row>
@@ -5372,6 +5567,11 @@
         </is>
       </c>
       <c r="O9" s="94" t="n"/>
+      <c r="Q9" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="126" customHeight="1" s="63">
       <c r="B10" s="77" t="inlineStr">
@@ -5441,6 +5641,11 @@
           <t>中国用天眼查，其他地区用 Dow Jones 查询公司经营范围、注册资本等</t>
         </is>
       </c>
+      <c r="Q10" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="72" customHeight="1" s="63">
       <c r="A11" s="89" t="inlineStr">
@@ -5513,6 +5718,11 @@
       <c r="O11" s="88" t="inlineStr">
         <is>
           <t>中国用天眼查，其他地区用 Dow Jones 查询公司经营范围、注册资本等</t>
+        </is>
+      </c>
+      <c r="Q11" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
         </is>
       </c>
     </row>
@@ -5581,6 +5791,11 @@
         </is>
       </c>
       <c r="O12" s="94" t="n"/>
+      <c r="Q12" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1" s="63">
       <c r="B13" s="91" t="inlineStr">
@@ -5647,6 +5862,11 @@
           <t>各国节假日查询工具</t>
         </is>
       </c>
+      <c r="Q13" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="108" customHeight="1" s="63">
       <c r="B14" s="77" t="inlineStr">
@@ -5711,6 +5931,11 @@
           <t>中国用天眼查，其他地区用 Dow Jones 查询公司经营范围、注册资本等</t>
         </is>
       </c>
+      <c r="Q14" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="54" customHeight="1" s="63">
       <c r="A15" s="89" t="inlineStr">
@@ -5774,6 +5999,11 @@
       <c r="P15" s="86" t="inlineStr">
         <is>
           <t>如何核验历史发票？</t>
+        </is>
+      </c>
+      <c r="Q15" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
         </is>
       </c>
     </row>
@@ -5802,6 +6032,11 @@
           <t>阈值是什么？</t>
         </is>
       </c>
+      <c r="Q17" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customFormat="1" customHeight="1" s="112">
       <c r="A18" s="89" t="n"/>
@@ -5828,6 +6063,11 @@
 突增：付款增长 500%。</t>
         </is>
       </c>
+      <c r="Q18" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="56" customFormat="1" customHeight="1" s="112">
       <c r="A19" s="89" t="n"/>
@@ -5848,6 +6088,11 @@
       </c>
       <c r="F19" s="89" t="n"/>
       <c r="G19" s="87" t="n"/>
+      <c r="Q19" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customFormat="1" customHeight="1" s="112">
       <c r="A20" s="89" t="n"/>
@@ -5868,6 +6113,11 @@
       </c>
       <c r="F20" s="89" t="n"/>
       <c r="G20" s="87" t="n"/>
+      <c r="Q20" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customFormat="1" customHeight="1" s="112">
       <c r="A21" s="89" t="n"/>
@@ -5888,6 +6138,11 @@
       </c>
       <c r="F21" s="89" t="n"/>
       <c r="G21" s="87" t="n"/>
+      <c r="Q21" s="138" t="inlineStr">
+        <is>
+          <t>采购侧</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="198" customFormat="1" customHeight="1" s="118">
       <c r="A26" s="71" t="inlineStr">
@@ -6108,7 +6363,7 @@
     <col width="39.6640625" customWidth="1" style="63" min="13" max="13"/>
     <col width="41.6640625" customWidth="1" style="63" min="14" max="14"/>
     <col hidden="1" width="26.83203125" customWidth="1" style="63" min="16" max="16"/>
-    <col width="8.83203125" customWidth="1" style="63" min="17" max="17"/>
+    <col width="22" customWidth="1" style="63" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="63">
@@ -6192,6 +6447,11 @@
           <t>Questions</t>
         </is>
       </c>
+      <c r="Q1" s="74" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="96" customHeight="1" s="63">
       <c r="B2" s="77" t="inlineStr">
@@ -6271,6 +6531,11 @@
 Sanctions list ( )</t>
         </is>
       </c>
+      <c r="Q2" s="138" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1" s="63">
       <c r="B3" s="77" t="inlineStr">
@@ -6348,7 +6613,11 @@
 Basel AML Index</t>
         </is>
       </c>
-      <c r="Q3" s="87" t="n"/>
+      <c r="Q3" s="138" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="64" customHeight="1" s="63">
       <c r="B4" s="77" t="inlineStr">
@@ -6419,6 +6688,11 @@
       <c r="O4" s="82" t="inlineStr">
         <is>
           <t>Offshore list (https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Glossary:List_of_offshore_financial_centres)</t>
+        </is>
+      </c>
+      <c r="Q4" s="138" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -6492,6 +6766,11 @@
       <c r="O5" s="88" t="inlineStr">
         <is>
           <t>Litigation lookup: Tianyancha for China, Dow Jones for ROW</t>
+        </is>
+      </c>
+      <c r="Q5" s="138" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -6567,6 +6846,11 @@
           <t>Tianyancha for China, Dow Jones for ROW</t>
         </is>
       </c>
+      <c r="Q6" s="138" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1" s="63">
       <c r="A7" s="89" t="inlineStr">
@@ -6644,6 +6928,11 @@
           <t>Principal place of business: Tianyancha for China, Dow Jones for ROW</t>
         </is>
       </c>
+      <c r="Q7" s="138" t="inlineStr">
+        <is>
+          <t>Both — currently payables only</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1" s="63">
       <c r="A8" s="89" t="inlineStr">
@@ -6724,6 +7013,11 @@
       <c r="P8" s="92" t="inlineStr">
         <is>
           <t>What is the difference from #7?</t>
+        </is>
+      </c>
+      <c r="Q8" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
         </is>
       </c>
     </row>
@@ -6786,6 +7080,11 @@
         </is>
       </c>
       <c r="O9" s="94" t="n"/>
+      <c r="Q9" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="126" customHeight="1" s="63">
       <c r="B10" s="77" t="inlineStr">
@@ -6855,6 +7154,11 @@
           <t>Business scope, registered capital etc.: Tianyancha for China, Dow Jones for ROW</t>
         </is>
       </c>
+      <c r="Q10" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="72" customHeight="1" s="63">
       <c r="A11" s="89" t="inlineStr">
@@ -6927,6 +7231,11 @@
       <c r="O11" s="88" t="inlineStr">
         <is>
           <t>Business scope, registered capital etc.: Tianyancha for China, Dow Jones for ROW</t>
+        </is>
+      </c>
+      <c r="Q11" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
         </is>
       </c>
     </row>
@@ -6995,6 +7304,11 @@
         </is>
       </c>
       <c r="O12" s="94" t="n"/>
+      <c r="Q12" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1" s="63">
       <c r="B13" s="77" t="inlineStr">
@@ -7061,6 +7375,11 @@
           <t>Public-holiday lookup tools per country</t>
         </is>
       </c>
+      <c r="Q13" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="108" customHeight="1" s="63">
       <c r="B14" s="77" t="inlineStr">
@@ -7125,6 +7444,11 @@
           <t>Business scope, registered capital etc.: Tianyancha for China, Dow Jones for ROW</t>
         </is>
       </c>
+      <c r="Q14" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="54" customHeight="1" s="63">
       <c r="A15" s="89" t="inlineStr">
@@ -7188,6 +7512,11 @@
       <c r="P15" s="86" t="inlineStr">
         <is>
           <t>How to verify historical invoices?</t>
+        </is>
+      </c>
+      <c r="Q15" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
         </is>
       </c>
     </row>
@@ -7216,6 +7545,11 @@
           <t>What is the threshold?</t>
         </is>
       </c>
+      <c r="Q17" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1" s="63">
       <c r="A18" s="89" t="n"/>
@@ -7242,6 +7576,11 @@
 Sudden surge: 500% payment increase.</t>
         </is>
       </c>
+      <c r="Q18" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="56" customHeight="1" s="63">
       <c r="A19" s="89" t="n"/>
@@ -7262,6 +7601,11 @@
       </c>
       <c r="F19" s="89" t="n"/>
       <c r="G19" s="87" t="n"/>
+      <c r="Q19" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customHeight="1" s="63">
       <c r="A20" s="89" t="n"/>
@@ -7282,6 +7626,11 @@
       </c>
       <c r="F20" s="89" t="n"/>
       <c r="G20" s="87" t="n"/>
+      <c r="Q20" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1" s="63">
       <c r="A21" s="89" t="n"/>
@@ -7302,6 +7651,11 @@
       </c>
       <c r="F21" s="89" t="n"/>
       <c r="G21" s="87" t="n"/>
+      <c r="Q21" s="138" t="inlineStr">
+        <is>
+          <t>Payables (vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="198" customHeight="1" s="63">
       <c r="A26" s="71" t="inlineStr">

--- a/docs/支付监控场景_中文版-0709-v2.xlsx
+++ b/docs/支付监控场景_中文版-0709-v2.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一些问题" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新-0709" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated-0709-EN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法务确认清单" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated-0709-EN" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'展示规则'!$A$1:$K$29</definedName>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -219,8 +220,23 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -279,8 +295,23 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -429,6 +460,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -445,7 +490,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -851,6 +896,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6345,6 +6411,566 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" style="63" min="1" max="1"/>
+    <col width="22" customWidth="1" style="63" min="2" max="2"/>
+    <col width="26" customWidth="1" style="63" min="3" max="3"/>
+    <col width="34" customWidth="1" style="63" min="4" max="4"/>
+    <col width="36" customWidth="1" style="63" min="5" max="5"/>
+    <col width="38" customWidth="1" style="63" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" s="63">
+      <c r="A1" s="139" t="inlineStr">
+        <is>
+          <t>行号</t>
+        </is>
+      </c>
+      <c r="B1" s="139" t="inlineStr">
+        <is>
+          <t>规则（活跃条目）</t>
+        </is>
+      </c>
+      <c r="C1" s="139" t="inlineStr">
+        <is>
+          <t>待确认项</t>
+        </is>
+      </c>
+      <c r="D1" s="139" t="inlineStr">
+        <is>
+          <t>数据候选（系统/字段）</t>
+        </is>
+      </c>
+      <c r="E1" s="139" t="inlineStr">
+        <is>
+          <t>我们的建议判断</t>
+        </is>
+      </c>
+      <c r="F1" s="139" t="inlineStr">
+        <is>
+          <t>请法务确认的问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="140" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B2" s="140" t="inlineStr">
+        <is>
+          <t>高风险辖区 / CPI</t>
+        </is>
+      </c>
+      <c r="C2" s="141" t="inlineStr">
+        <is>
+          <t>① "交易对手所在国"指哪个国别
+② CPI 多低算高风险
+③ 高风险辖区名单的维护</t>
+        </is>
+      </c>
+      <c r="D2" s="141" t="inlineStr">
+        <is>
+          <t>候选国别：a.供应商注册国（S4 BP）b.营业地 c.发票开具国（Ariba/LGAP 发票）d.收款银行国（S4 SWIFT 解析）</t>
+        </is>
+      </c>
+      <c r="E2" s="141" t="inlineStr">
+        <is>
+          <t>四个国别都查，任一命中即触发；CPI 阈值建议 &lt;40 分；名单由 Brenda 年度更新（原表已注）</t>
+        </is>
+      </c>
+      <c r="F2" s="141" t="inlineStr">
+        <is>
+          <t>① 四国别口径是否认可，还是只查其中某几个？② CPI 阈值定多少？③ 名单更新频率与责任人确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="140" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B3" s="140" t="inlineStr">
+        <is>
+          <t>FATF / 制裁辖区</t>
+        </is>
+      </c>
+      <c r="C3" s="141" t="inlineStr">
+        <is>
+          <t>① 黑名单、灰名单是否都触发
+② "经济制裁法律"指哪些体系</t>
+        </is>
+      </c>
+      <c r="D3" s="141" t="inlineStr">
+        <is>
+          <t>国别来源同上；名单：FATF 黑/灰名单（官网）；制裁体系候选：OFAC（美）/ EU / UN / 中国商务部</t>
+        </is>
+      </c>
+      <c r="E3" s="141" t="inlineStr">
+        <is>
+          <t>黑名单+灰名单都触发（灰名单可标记为较低优先级）；制裁体系以 OFAC+EU+UN 为基础</t>
+        </is>
+      </c>
+      <c r="F3" s="141" t="inlineStr">
+        <is>
+          <t>① 灰名单是否与黑名单同级处理？② 制裁法律体系范围（原表 K3 遗留问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="140" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B4" s="140" t="inlineStr">
+        <is>
+          <t>避税天堂 / 离岸中转</t>
+        </is>
+      </c>
+      <c r="C4" s="141" t="inlineStr">
+        <is>
+          <t>★ 重大歧义："中转"查什么路径
+② 离岸名单用哪个</t>
+        </is>
+      </c>
+      <c r="D4" s="141" t="inlineStr">
+        <is>
+          <t>a.货物运输路径：Ariba PO 仅有 ship-from/to（完整路径需物流 TMS，暂无）
+b.资金路径：收款银行/中转行国别（S4/SWIFT）</t>
+        </is>
+      </c>
+      <c r="E4" s="141" t="inlineStr">
+        <is>
+          <t>倾向先做【资金路径】（收款行+中转行在离岸辖区）——数据可得且更贴近洗钱本质；货物路径先用 PO 起终点近似；名单用原表给的 EU 离岸金融中心清单</t>
+        </is>
+      </c>
+      <c r="F4" s="141" t="inlineStr">
+        <is>
+          <t>① 查资金路径还是货物路径，还是两者？② 只有起终点（无完整路径）法务是否接受？③ 离岸名单确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="140" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B5" s="140" t="inlineStr">
+        <is>
+          <t>刑事/民事/监管诉讼</t>
+        </is>
+      </c>
+      <c r="C5" s="141" t="inlineStr">
+        <is>
+          <t>① 诉讼类型与时间窗
+② 查公司还是也查股东/董监高
+③ "联想已知"的内部记录在哪</t>
+        </is>
+      </c>
+      <c r="D5" s="141" t="inlineStr">
+        <is>
+          <t>外部：天眼查（中国）/ DJ（海外）诉讼库；内部：腐败关联方历史付款记录（S4 AP 历史）——但"已知腐败方"名单目前不存在</t>
+        </is>
+      </c>
+      <c r="E5" s="141" t="inlineStr">
+        <is>
+          <t>仅腐败/欺诈/洗钱相关诉讼，近 5 年；查公司+法定代表人+控股股东；内部名单待建</t>
+        </is>
+      </c>
+      <c r="F5" s="141" t="inlineStr">
+        <is>
+          <t>① 诉讼类型与年限？② 主体穿透范围？③ 内部"已知腐败方"记录归哪个部门维护？</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="140" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B6" s="140" t="inlineStr">
+        <is>
+          <t>负面媒体（PEP）</t>
+        </is>
+      </c>
+      <c r="C6" s="141" t="inlineStr">
+        <is>
+          <t>① 股东穿透层数与持股阈值
+② PEP 库来源
+③ 高风险辖区 PEP 是否加重</t>
+        </is>
+      </c>
+      <c r="D6" s="141" t="inlineStr">
+        <is>
+          <t>穿透：天眼查股权（中国）/ DJ（海外）；PEP 库：DJ PEP 数据；角色清单原表 D6 已列（控股股东/法代/董监高等）</t>
+        </is>
+      </c>
+      <c r="E6" s="141" t="inlineStr">
+        <is>
+          <t>穿透 2 层、持股 ≥10% 或任 D6 所列职务即查；命中 PEP 即触发，高风险辖区 PEP 在调查阶段加重</t>
+        </is>
+      </c>
+      <c r="F6" s="141" t="inlineStr">
+        <is>
+          <t>① 穿透层数与持股比例阈值？② 只用 DJ 的 PEP 库是否足够（中国政要覆盖）？</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="140" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B7" s="140" t="inlineStr">
+        <is>
+          <t>A1 银行属地≠主要经营地（准确率100%）</t>
+        </is>
+      </c>
+      <c r="C7" s="141" t="inlineStr">
+        <is>
+          <t>① "主要经营地"指注册国还是实际经营地
+② 银行属地的取数</t>
+        </is>
+      </c>
+      <c r="D7" s="141" t="inlineStr">
+        <is>
+          <t>主要经营地候选：a.注册国（S4 BP，内部可得）b.实际经营地（天眼查/DJ，外部）
+银行属地：收款账户 SWIFT 代码前缀解析（S4 付款凭证）</t>
+        </is>
+      </c>
+      <c r="E7" s="141" t="inlineStr">
+        <is>
+          <t>检测阶段用【注册国】（确定性高、可自动化）；实际经营地留给调查阶段核实；银行属地以 SWIFT 解析为准</t>
+        </is>
+      </c>
+      <c r="F7" s="141" t="inlineStr">
+        <is>
+          <t>① 经营地以注册国为准是否可接受？两者不一致时听谁的？② 一个供应商多个收款账户时逐账户判断？</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="140" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B8" s="140" t="inlineStr">
+        <is>
+          <t>A2 付款方国≠发票开具地（准确率100%）</t>
+        </is>
+      </c>
+      <c r="C8" s="141" t="inlineStr">
+        <is>
+          <t>★ "发票开具地"具体指发票上哪个字段
+② 与第 7 条（R7）的边界</t>
+        </is>
+      </c>
+      <c r="D8" s="141" t="inlineStr">
+        <is>
+          <t>候选：a.开票方注册地址国 b.remit-to 汇款地址国 c.税号归属国（VAT 前缀）
+付款方国：联想付款主体 company code 所属国（S4）</t>
+        </is>
+      </c>
+      <c r="E8" s="141" t="inlineStr">
+        <is>
+          <t>建议以【开票方地址国】为主判据，税号国做交叉校验；R7 查"银行vs供应商"，R8 查"付款主体vs发票"，维度不同（原表 P8 问题的答案）</t>
+        </is>
+      </c>
+      <c r="F8" s="141" t="inlineStr">
+        <is>
+          <t>① 开具地=开票方地址？税号国不一致时如何处理？② 认可 R7/R8 的边界划分吗？③ LGAP 附件发票需 OCR 提取，接受吗？置信度要求？</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="142" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="B9" s="142" t="inlineStr">
+        <is>
+          <t>无 PO/合同/汇款明细的付款</t>
+        </is>
+      </c>
+      <c r="C9" s="143" t="inlineStr">
+        <is>
+          <t>DT 已注"仅 LGAP、属正常场景"——那这条还告警吗</t>
+        </is>
+      </c>
+      <c r="D9" s="143" t="inlineStr">
+        <is>
+          <t>LGAP 付款申请记录（该场景仅存在于 LGAP）</t>
+        </is>
+      </c>
+      <c r="E9" s="143" t="inlineStr">
+        <is>
+          <t>不单独告警，仅作为付款的风险特征参与评分（无 PO = 少一道三单匹配防线）</t>
+        </is>
+      </c>
+      <c r="F9" s="143" t="inlineStr">
+        <is>
+          <t>确认：只记录不告警？还是特定费用类别之外的无 PO 付款仍要告警？</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="142" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B10" s="142" t="inlineStr">
+        <is>
+          <t>资源与活动规模不相称</t>
+        </is>
+      </c>
+      <c r="C10" s="143" t="inlineStr">
+        <is>
+          <t>① 比例阈值
+② 历史窗口
+③ 海外无"注册资本"概念用什么替代</t>
+        </is>
+      </c>
+      <c r="D10" s="143" t="inlineStr">
+        <is>
+          <t>注册资本：天眼查（中国）/ DJ（海外，部分国家缺失）；历史 PO：Ariba；历史付款：S4 AP</t>
+        </is>
+      </c>
+      <c r="E10" s="143" t="inlineStr">
+        <is>
+          <t>建议：滚动 12 个月累计付款 &gt; 注册资本 × 10 触发（阈值可调）；海外缺注册资本时用员工数/营收区间替代或跳过</t>
+        </is>
+      </c>
+      <c r="F10" s="143" t="inlineStr">
+        <is>
+          <t>① 倍数阈值定多少？② 窗口 12 个月可以吗？③ 海外替代口径认可吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="140" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B11" s="140" t="inlineStr">
+        <is>
+          <t>A3 主营业务≠PO品类（准确率100%）</t>
+        </is>
+      </c>
+      <c r="C11" s="141" t="inlineStr">
+        <is>
+          <t>① "不相关"的判定标准
+② 品类粒度
+③ LLM 语义判定是否可接受</t>
+        </is>
+      </c>
+      <c r="D11" s="141" t="inlineStr">
+        <is>
+          <t>经营范围：天眼查/DJ；品类：Ariba commodity code（UNSPSC 树，可选大类或细类层级）</t>
+        </is>
+      </c>
+      <c r="E11" s="141" t="inlineStr">
+        <is>
+          <t>用 LLM 做语义相关性判定，低于阈值触发；品类先用大类层级（误报少）；判定结果附解释供复核</t>
+        </is>
+      </c>
+      <c r="F11" s="141" t="inlineStr">
+        <is>
+          <t>① 接受 LLM 判定吗？需要多高置信度？② 品类用大类还是细类？③ 贸易类公司（经营范围极宽）如何处理？</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="142" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B12" s="142" t="inlineStr">
+        <is>
+          <t>对新供应商付款突增</t>
+        </is>
+      </c>
+      <c r="C12" s="143" t="inlineStr">
+        <is>
+          <t>① 500% 的基线是什么
+② 单笔还是累计
+③ "新"的起点</t>
+        </is>
+      </c>
+      <c r="D12" s="143" t="inlineStr">
+        <is>
+          <t>入库日期：S4 BP / Ariba SLP；付款流水：S4（全渠道含 LGAP）</t>
+        </is>
+      </c>
+      <c r="E12" s="143" t="inlineStr">
+        <is>
+          <t>新=入库 12 个月内（DT 注）；基线=该供应商此前 6 个月月均付款；月累计 &gt; 基线×5 触发；无历史（首单即大额）另设绝对阈值</t>
+        </is>
+      </c>
+      <c r="F12" s="143" t="inlineStr">
+        <is>
+          <t>① 基线口径认可吗？② 首单大额的绝对阈值定多少？③ 500% 是 DT 建议值，法务认可吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="142" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B13" s="142" t="inlineStr">
+        <is>
+          <t>周末/节假日交易</t>
+        </is>
+      </c>
+      <c r="C13" s="143" t="inlineStr">
+        <is>
+          <t>① 以哪个日期为准
+② 以哪国日历为准</t>
+        </is>
+      </c>
+      <c r="D13" s="143" t="inlineStr">
+        <is>
+          <t>候选日期：a.付款执行日（S4 清账日）b.发票日期 c.付款申请日（LGAP/Ariba）
+日历：付款方所在国（原表 O13 已倾向 payer side）</t>
+        </is>
+      </c>
+      <c r="E13" s="143" t="inlineStr">
+        <is>
+          <t>用【付款执行日】（实际资金动作；申请日/发票日会误报）；日历按付款方所在国</t>
+        </is>
+      </c>
+      <c r="F13" s="143" t="inlineStr">
+        <is>
+          <t>① 日期口径确认？② 付款方=联想付款主体所在国，还是收款方所在国？（原表写 payer 但值得再确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="142" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B14" s="142" t="inlineStr">
+        <is>
+          <t>汇入无明显关联账户</t>
+        </is>
+      </c>
+      <c r="C14" s="143" t="inlineStr">
+        <is>
+          <t>① "明显关联"的定义
+② 此条是否保留（取决于 LGAP 系统管控）</t>
+        </is>
+      </c>
+      <c r="D14" s="143" t="inlineStr">
+        <is>
+          <t>登记账户：S4 供应商主数据的银行账户；实际收款账户：付款申请/凭证；关联判定：天眼查/DJ 股权关系</t>
+        </is>
+      </c>
+      <c r="E14" s="143" t="inlineStr">
+        <is>
+          <t>关联=同一实体或持股 ≥50% 的关联公司（原表 K14 自己提的问法）；若 DT 确认 LGAP 已硬管控则此条移除</t>
+        </is>
+      </c>
+      <c r="F14" s="143" t="inlineStr">
+        <is>
+          <t>① 关联阈值 50% 认可吗？集团财务公司代收算关联吗？② 等 DT 结论后决定去留</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="140" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B15" s="140" t="inlineStr">
+        <is>
+          <t>A4 虚假发票（准确率100%）</t>
+        </is>
+      </c>
+      <c r="C15" s="141" t="inlineStr">
+        <is>
+          <t>① "虚假"的判定手段（中外不同）
+② 历史发票如何核验
+③ 发票影像可得性</t>
+        </is>
+      </c>
+      <c r="D15" s="141" t="inlineStr">
+        <is>
+          <t>中国：税局增值税发票查验平台；海外：发票号去重（S4 AP 历史）+ 模板/字段异常检测；影像：Ariba Network / LGAP 附件</t>
+        </is>
+      </c>
+      <c r="E15" s="141" t="inlineStr">
+        <is>
+          <t>中国走税局查验（硬判据）；海外先做重复号+连号+字段异常三项（软判据，命中转人工）</t>
+        </is>
+      </c>
+      <c r="F15" s="141" t="inlineStr">
+        <is>
+          <t>① 海外"虚假"以哪些特征为准？软判据也算 T1 吗？② 历史发票核验范围（回溯多久）？③ 查验不通过是否直接=欺诈结论？</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="144" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="B16" s="144" t="inlineStr">
+        <is>
+          <t>跨规则统一口径</t>
+        </is>
+      </c>
+      <c r="C16" s="145" t="inlineStr">
+        <is>
+          <t>① 金额阈值的币种折算
+② 国别字段优先级
+③ 复核时限的日历口径</t>
+        </is>
+      </c>
+      <c r="D16" s="145" t="inlineStr">
+        <is>
+          <t>多币种付款（S4 有交易币种与本位币）；多个国别字段可能互相矛盾</t>
+        </is>
+      </c>
+      <c r="E16" s="145" t="inlineStr">
+        <is>
+          <t>金额统一折算 USD（按付款日汇率）；国别矛盾时优先级：银行国 &gt; 发票国 &gt; 注册国（供讨论）；SLA 按自然日</t>
+        </is>
+      </c>
+      <c r="F16" s="145" t="inlineStr">
+        <is>
+          <t>① 币种口径？② 国别优先级？③ T1 的 24 小时按自然日还是工作日？</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/支付监控场景_中文版-0709-v2.xlsx
+++ b/docs/支付监控场景_中文版-0709-v2.xlsx
@@ -13,8 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一些问题" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新-0709" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法务确认清单" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated-0709-EN" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated-0709-EN" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'展示规则'!$A$1:$K$29</definedName>
@@ -490,7 +489,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -919,6 +918,10 @@
     <xf numFmtId="0" fontId="28" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4898,7 +4901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="7.1640625" customWidth="1" style="76" min="1" max="1"/>
@@ -4917,6 +4920,8 @@
     <col width="41.6640625" customWidth="1" style="84" min="14" max="15"/>
     <col hidden="1" width="26.83203125" customWidth="1" style="84" min="16" max="16"/>
     <col width="18" customWidth="1" style="112" min="17" max="16384"/>
+    <col width="52" customWidth="1" style="63" min="18" max="18"/>
+    <col width="40" customWidth="1" style="63" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="63">
@@ -5005,6 +5010,16 @@
           <t>适用方向</t>
         </is>
       </c>
+      <c r="R1" s="74" t="inlineStr">
+        <is>
+          <t>法务确认 · 建议口径</t>
+        </is>
+      </c>
+      <c r="S1" s="74" t="inlineStr">
+        <is>
+          <t>法务确认 · 待拍板问题</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="96" customHeight="1" s="63">
       <c r="B2" s="77" t="inlineStr">
@@ -5089,6 +5104,20 @@
           <t>双向</t>
         </is>
       </c>
+      <c r="R2" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①国别口径 ②CPI 阈值 ③名单维护
+候选：注册国(S4 BP)/营业地/发票国(Ariba|LGAP)/银行国(SWIFT解析)
+建议：四国别都查，任一命中即触发；CPI &lt;40 算高风险；名单 Brenda 年度更新</t>
+        </is>
+      </c>
+      <c r="S2" s="146" t="inlineStr">
+        <is>
+          <t>① 四国别口径认可？还是只查部分？
+② CPI 阈值定多少？
+③ 名单更新频率与责任人</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1" s="63">
       <c r="B3" s="77" t="inlineStr">
@@ -5171,6 +5200,18 @@
           <t>双向</t>
         </is>
       </c>
+      <c r="R3" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①灰名单是否同级触发 ②制裁体系范围
+建议：黑+灰名单都触发（灰名单优先级略低）；制裁体系以 OFAC+EU+UN 为基础</t>
+        </is>
+      </c>
+      <c r="S3" s="146" t="inlineStr">
+        <is>
+          <t>① 灰名单与黑名单同级处理？
+② "经济制裁法律"指哪些体系（K3 遗留问题）</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="64" customHeight="1" s="63">
       <c r="B4" s="77" t="inlineStr">
@@ -5246,6 +5287,20 @@
       <c r="Q4" s="138" t="inlineStr">
         <is>
           <t>双向</t>
+        </is>
+      </c>
+      <c r="R4" s="146" t="inlineStr">
+        <is>
+          <t>★重大歧义："中转"查什么路径
+候选：a.货物路径（Ariba PO 仅有起运/目的地，完整路径需物流TMS，暂无）b.资金路径（收款行/中转行国别，S4/SWIFT，数据可得）
+建议：先做资金路径（更贴洗钱本质）；货物路径用 PO 起终点近似；名单用 EU 离岸金融中心清单</t>
+        </is>
+      </c>
+      <c r="S4" s="146" t="inlineStr">
+        <is>
+          <t>① 查资金路径还是货物路径，还是两者？
+② 只有起终点（无完整路径）是否接受？
+③ 离岸名单确认</t>
         </is>
       </c>
     </row>
@@ -5324,6 +5379,20 @@
       <c r="Q5" s="138" t="inlineStr">
         <is>
           <t>双向</t>
+        </is>
+      </c>
+      <c r="R5" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①诉讼类型与时间窗 ②主体范围 ③内部记录
+候选：天眼查(中国)/DJ(海外)诉讼库；内部腐败方付款记录（S4 AP 历史，但"已知腐败方"名单目前不存在）
+建议：仅腐败/欺诈/洗钱相关，近 5 年；查公司+法代+控股股东</t>
+        </is>
+      </c>
+      <c r="S5" s="146" t="inlineStr">
+        <is>
+          <t>① 诉讼类型与年限？
+② 主体穿透范围？
+③ 内部"已知腐败方"名单归哪个部门维护？</t>
         </is>
       </c>
     </row>
@@ -5404,6 +5473,19 @@
           <t>双向</t>
         </is>
       </c>
+      <c r="R6" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①穿透层数与持股阈值 ②PEP 库来源
+候选：天眼查股权(中国)/DJ(海外)；PEP 库=DJ；角色清单见 D6
+建议：穿透 2 层；持股≥10% 或任 D6 所列职务即查；高风险辖区 PEP 调查阶段加重</t>
+        </is>
+      </c>
+      <c r="S6" s="146" t="inlineStr">
+        <is>
+          <t>① 穿透层数与持股比例阈值？
+② 只用 DJ 的 PEP 库，中国政要覆盖是否足够？</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1" s="63">
       <c r="A7" s="89" t="inlineStr">
@@ -5486,6 +5568,19 @@
           <t>双向（当前仅实施采购侧）</t>
         </is>
       </c>
+      <c r="R7" s="146" t="inlineStr">
+        <is>
+          <t>待确认："主要经营地"=注册国还是实际经营地
+候选：a.注册国（S4 BP，内部可得）b.实际经营地（天眼查/DJ）
+建议：检测阶段用注册国（可自动化）；实际经营地留调查阶段；银行属地以收款账户 SWIFT 前缀解析（S4）</t>
+        </is>
+      </c>
+      <c r="S7" s="146" t="inlineStr">
+        <is>
+          <t>① 经营地以注册国为准可接受？两者不一致听谁的？
+② 供应商多个收款账户时逐账户判断？</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1" s="63">
       <c r="A8" s="89" t="inlineStr">
@@ -5571,6 +5666,20 @@
       <c r="Q8" s="138" t="inlineStr">
         <is>
           <t>采购侧</t>
+        </is>
+      </c>
+      <c r="R8" s="146" t="inlineStr">
+        <is>
+          <t>★"发票开具地"=发票上哪个字段
+候选：a.开票方地址国 b.remit-to 汇款地址国 c.税号归属国（VAT 前缀）；付款方国=联想 company code 所属国（S4）
+建议：以开票方地址国为主判据，税号国交叉校验；与 R7 边界：R7 查银行vs供应商，R8 查付款主体vs发票（P8 问题的答案）</t>
+        </is>
+      </c>
+      <c r="S8" s="146" t="inlineStr">
+        <is>
+          <t>① "开具地"=开票方地址？税号国不一致时如何处理？
+② 认可与第 7 行的边界划分？
+③ LGAP 附件发票需 OCR 提取，接受吗？置信度要求？</t>
         </is>
       </c>
     </row>
@@ -5636,6 +5745,17 @@
       <c r="Q9" s="138" t="inlineStr">
         <is>
           <t>采购侧</t>
+        </is>
+      </c>
+      <c r="R9" s="146" t="inlineStr">
+        <is>
+          <t>DT 已注"仅 LGAP、正常场景"
+建议：不单独告警，仅作为风险特征参与评分（无 PO=少一道三单匹配防线）</t>
+        </is>
+      </c>
+      <c r="S9" s="146" t="inlineStr">
+        <is>
+          <t>确认：只记录不告警？还是特定费用类别之外的无 PO 付款仍要告警？</t>
         </is>
       </c>
     </row>
@@ -5712,6 +5832,20 @@
           <t>采购侧</t>
         </is>
       </c>
+      <c r="R10" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①倍数阈值 ②窗口 ③海外无注册资本概念
+候选：注册资本=天眼查/DJ（海外部分国家缺失）；历史 PO=Ariba；付款=S4 AP
+建议：滚动 12 个月累计付款 &gt; 注册资本×10 触发；海外缺失时用员工数/营收区间替代或跳过</t>
+        </is>
+      </c>
+      <c r="S10" s="146" t="inlineStr">
+        <is>
+          <t>① 倍数阈值定多少？
+② 12 个月窗口可以吗？
+③ 海外替代口径认可吗？</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="72" customHeight="1" s="63">
       <c r="A11" s="89" t="inlineStr">
@@ -5789,6 +5923,20 @@
       <c r="Q11" s="138" t="inlineStr">
         <is>
           <t>采购侧</t>
+        </is>
+      </c>
+      <c r="R11" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①"不相关"判定标准 ②品类粒度 ③LLM 判定可否
+候选：经营范围=天眼查/DJ；品类=Ariba commodity code（UNSPSC 树）
+建议：LLM 语义相关性判定+附解释；品类先用大类层级（误报少）</t>
+        </is>
+      </c>
+      <c r="S11" s="146" t="inlineStr">
+        <is>
+          <t>① 接受 LLM 判定吗？置信度要求？
+② 品类用大类还是细类？
+③ 贸易类公司（经营范围极宽）如何处理？</t>
         </is>
       </c>
     </row>
@@ -5862,6 +6010,20 @@
           <t>采购侧</t>
         </is>
       </c>
+      <c r="R12" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①基线口径 ②单笔还是累计 ③首单大额
+候选：入库日期=S4 BP/Ariba SLP；流水=S4（含 LGAP 通道）
+建议：新=入库 12 个月内；基线=此前 6 个月月均；月累计&gt;基线×5 触发；首单即大额另设绝对阈值</t>
+        </is>
+      </c>
+      <c r="S12" s="146" t="inlineStr">
+        <is>
+          <t>① 基线口径认可？
+② 首单大额的绝对阈值定多少？
+③ 500%（DT 建议值）法务认可吗？</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1" s="63">
       <c r="B13" s="91" t="inlineStr">
@@ -5933,6 +6095,19 @@
           <t>采购侧</t>
         </is>
       </c>
+      <c r="R13" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①以哪个日期为准 ②哪国日历
+候选：a.付款执行日（S4 清账日）b.发票日期 c.申请日（LGAP/Ariba）
+建议：用付款执行日（实际资金动作，申请日/发票日会误报）；日历按付款方所在国（O13 已倾向 payer side）</t>
+        </is>
+      </c>
+      <c r="S13" s="146" t="inlineStr">
+        <is>
+          <t>① 日期口径确认？
+② 付款方=联想付款主体所在国，确认？</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="108" customHeight="1" s="63">
       <c r="B14" s="77" t="inlineStr">
@@ -6002,6 +6177,19 @@
           <t>采购侧</t>
         </is>
       </c>
+      <c r="R14" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①"明显关联"定义 ②此条去留
+候选：登记账户=S4 供应商主数据；实际收款账户=付款申请/凭证；关联判定=天眼查/DJ 股权
+建议：关联=同一实体或持股≥50% 关联公司（K14 自提问法）；若 DT 确认 LGAP 已硬管控则移除</t>
+        </is>
+      </c>
+      <c r="S14" s="146" t="inlineStr">
+        <is>
+          <t>① 关联阈值 50% 认可？集团财务公司代收算关联吗？
+② 等 DT 结论后决定去留</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="54" customHeight="1" s="63">
       <c r="A15" s="89" t="inlineStr">
@@ -6070,6 +6258,20 @@
       <c r="Q15" s="138" t="inlineStr">
         <is>
           <t>采购侧</t>
+        </is>
+      </c>
+      <c r="R15" s="146" t="inlineStr">
+        <is>
+          <t>待确认：①中外"虚假"判定手段 ②历史发票核验 ③影像可得性
+候选：中国=税局查验平台（硬判据）；海外=发票号去重（S4 AP）+连号+模板/字段异常（软判据）；影像=Ariba Network/LGAP 附件
+建议：中国走税局查验；海外三项软判据命中转人工</t>
+        </is>
+      </c>
+      <c r="S15" s="146" t="inlineStr">
+        <is>
+          <t>① 海外软判据也算 T1 吗？
+② 历史发票回溯多久？
+③ 查验不通过是否直接=欺诈结论？</t>
         </is>
       </c>
     </row>
@@ -6207,6 +6409,26 @@
       <c r="Q21" s="138" t="inlineStr">
         <is>
           <t>采购侧</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="147" t="inlineStr">
+        <is>
+          <t>跨规则通用</t>
+        </is>
+      </c>
+      <c r="R23" s="146" t="inlineStr">
+        <is>
+          <t>跨规则通用口径
+建议：金额统一折算 USD（按付款日汇率）；国别矛盾时优先级 银行国&gt;发票国&gt;注册国（供讨论）；SLA 按自然日</t>
+        </is>
+      </c>
+      <c r="S23" s="146" t="inlineStr">
+        <is>
+          <t>① 币种折算口径？
+② 国别字段优先级？
+③ T1 的 24 小时按自然日还是工作日？</t>
         </is>
       </c>
     </row>
@@ -6406,566 +6628,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" style="63" min="1" max="1"/>
-    <col width="22" customWidth="1" style="63" min="2" max="2"/>
-    <col width="26" customWidth="1" style="63" min="3" max="3"/>
-    <col width="34" customWidth="1" style="63" min="4" max="4"/>
-    <col width="36" customWidth="1" style="63" min="5" max="5"/>
-    <col width="38" customWidth="1" style="63" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1" s="63">
-      <c r="A1" s="139" t="inlineStr">
-        <is>
-          <t>行号</t>
-        </is>
-      </c>
-      <c r="B1" s="139" t="inlineStr">
-        <is>
-          <t>规则（活跃条目）</t>
-        </is>
-      </c>
-      <c r="C1" s="139" t="inlineStr">
-        <is>
-          <t>待确认项</t>
-        </is>
-      </c>
-      <c r="D1" s="139" t="inlineStr">
-        <is>
-          <t>数据候选（系统/字段）</t>
-        </is>
-      </c>
-      <c r="E1" s="139" t="inlineStr">
-        <is>
-          <t>我们的建议判断</t>
-        </is>
-      </c>
-      <c r="F1" s="139" t="inlineStr">
-        <is>
-          <t>请法务确认的问题</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="140" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B2" s="140" t="inlineStr">
-        <is>
-          <t>高风险辖区 / CPI</t>
-        </is>
-      </c>
-      <c r="C2" s="141" t="inlineStr">
-        <is>
-          <t>① "交易对手所在国"指哪个国别
-② CPI 多低算高风险
-③ 高风险辖区名单的维护</t>
-        </is>
-      </c>
-      <c r="D2" s="141" t="inlineStr">
-        <is>
-          <t>候选国别：a.供应商注册国（S4 BP）b.营业地 c.发票开具国（Ariba/LGAP 发票）d.收款银行国（S4 SWIFT 解析）</t>
-        </is>
-      </c>
-      <c r="E2" s="141" t="inlineStr">
-        <is>
-          <t>四个国别都查，任一命中即触发；CPI 阈值建议 &lt;40 分；名单由 Brenda 年度更新（原表已注）</t>
-        </is>
-      </c>
-      <c r="F2" s="141" t="inlineStr">
-        <is>
-          <t>① 四国别口径是否认可，还是只查其中某几个？② CPI 阈值定多少？③ 名单更新频率与责任人确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="140" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="B3" s="140" t="inlineStr">
-        <is>
-          <t>FATF / 制裁辖区</t>
-        </is>
-      </c>
-      <c r="C3" s="141" t="inlineStr">
-        <is>
-          <t>① 黑名单、灰名单是否都触发
-② "经济制裁法律"指哪些体系</t>
-        </is>
-      </c>
-      <c r="D3" s="141" t="inlineStr">
-        <is>
-          <t>国别来源同上；名单：FATF 黑/灰名单（官网）；制裁体系候选：OFAC（美）/ EU / UN / 中国商务部</t>
-        </is>
-      </c>
-      <c r="E3" s="141" t="inlineStr">
-        <is>
-          <t>黑名单+灰名单都触发（灰名单可标记为较低优先级）；制裁体系以 OFAC+EU+UN 为基础</t>
-        </is>
-      </c>
-      <c r="F3" s="141" t="inlineStr">
-        <is>
-          <t>① 灰名单是否与黑名单同级处理？② 制裁法律体系范围（原表 K3 遗留问题）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="140" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="B4" s="140" t="inlineStr">
-        <is>
-          <t>避税天堂 / 离岸中转</t>
-        </is>
-      </c>
-      <c r="C4" s="141" t="inlineStr">
-        <is>
-          <t>★ 重大歧义："中转"查什么路径
-② 离岸名单用哪个</t>
-        </is>
-      </c>
-      <c r="D4" s="141" t="inlineStr">
-        <is>
-          <t>a.货物运输路径：Ariba PO 仅有 ship-from/to（完整路径需物流 TMS，暂无）
-b.资金路径：收款银行/中转行国别（S4/SWIFT）</t>
-        </is>
-      </c>
-      <c r="E4" s="141" t="inlineStr">
-        <is>
-          <t>倾向先做【资金路径】（收款行+中转行在离岸辖区）——数据可得且更贴近洗钱本质；货物路径先用 PO 起终点近似；名单用原表给的 EU 离岸金融中心清单</t>
-        </is>
-      </c>
-      <c r="F4" s="141" t="inlineStr">
-        <is>
-          <t>① 查资金路径还是货物路径，还是两者？② 只有起终点（无完整路径）法务是否接受？③ 离岸名单确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="140" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="B5" s="140" t="inlineStr">
-        <is>
-          <t>刑事/民事/监管诉讼</t>
-        </is>
-      </c>
-      <c r="C5" s="141" t="inlineStr">
-        <is>
-          <t>① 诉讼类型与时间窗
-② 查公司还是也查股东/董监高
-③ "联想已知"的内部记录在哪</t>
-        </is>
-      </c>
-      <c r="D5" s="141" t="inlineStr">
-        <is>
-          <t>外部：天眼查（中国）/ DJ（海外）诉讼库；内部：腐败关联方历史付款记录（S4 AP 历史）——但"已知腐败方"名单目前不存在</t>
-        </is>
-      </c>
-      <c r="E5" s="141" t="inlineStr">
-        <is>
-          <t>仅腐败/欺诈/洗钱相关诉讼，近 5 年；查公司+法定代表人+控股股东；内部名单待建</t>
-        </is>
-      </c>
-      <c r="F5" s="141" t="inlineStr">
-        <is>
-          <t>① 诉讼类型与年限？② 主体穿透范围？③ 内部"已知腐败方"记录归哪个部门维护？</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="140" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="B6" s="140" t="inlineStr">
-        <is>
-          <t>负面媒体（PEP）</t>
-        </is>
-      </c>
-      <c r="C6" s="141" t="inlineStr">
-        <is>
-          <t>① 股东穿透层数与持股阈值
-② PEP 库来源
-③ 高风险辖区 PEP 是否加重</t>
-        </is>
-      </c>
-      <c r="D6" s="141" t="inlineStr">
-        <is>
-          <t>穿透：天眼查股权（中国）/ DJ（海外）；PEP 库：DJ PEP 数据；角色清单原表 D6 已列（控股股东/法代/董监高等）</t>
-        </is>
-      </c>
-      <c r="E6" s="141" t="inlineStr">
-        <is>
-          <t>穿透 2 层、持股 ≥10% 或任 D6 所列职务即查；命中 PEP 即触发，高风险辖区 PEP 在调查阶段加重</t>
-        </is>
-      </c>
-      <c r="F6" s="141" t="inlineStr">
-        <is>
-          <t>① 穿透层数与持股比例阈值？② 只用 DJ 的 PEP 库是否足够（中国政要覆盖）？</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="140" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="B7" s="140" t="inlineStr">
-        <is>
-          <t>A1 银行属地≠主要经营地（准确率100%）</t>
-        </is>
-      </c>
-      <c r="C7" s="141" t="inlineStr">
-        <is>
-          <t>① "主要经营地"指注册国还是实际经营地
-② 银行属地的取数</t>
-        </is>
-      </c>
-      <c r="D7" s="141" t="inlineStr">
-        <is>
-          <t>主要经营地候选：a.注册国（S4 BP，内部可得）b.实际经营地（天眼查/DJ，外部）
-银行属地：收款账户 SWIFT 代码前缀解析（S4 付款凭证）</t>
-        </is>
-      </c>
-      <c r="E7" s="141" t="inlineStr">
-        <is>
-          <t>检测阶段用【注册国】（确定性高、可自动化）；实际经营地留给调查阶段核实；银行属地以 SWIFT 解析为准</t>
-        </is>
-      </c>
-      <c r="F7" s="141" t="inlineStr">
-        <is>
-          <t>① 经营地以注册国为准是否可接受？两者不一致时听谁的？② 一个供应商多个收款账户时逐账户判断？</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="140" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="B8" s="140" t="inlineStr">
-        <is>
-          <t>A2 付款方国≠发票开具地（准确率100%）</t>
-        </is>
-      </c>
-      <c r="C8" s="141" t="inlineStr">
-        <is>
-          <t>★ "发票开具地"具体指发票上哪个字段
-② 与第 7 条（R7）的边界</t>
-        </is>
-      </c>
-      <c r="D8" s="141" t="inlineStr">
-        <is>
-          <t>候选：a.开票方注册地址国 b.remit-to 汇款地址国 c.税号归属国（VAT 前缀）
-付款方国：联想付款主体 company code 所属国（S4）</t>
-        </is>
-      </c>
-      <c r="E8" s="141" t="inlineStr">
-        <is>
-          <t>建议以【开票方地址国】为主判据，税号国做交叉校验；R7 查"银行vs供应商"，R8 查"付款主体vs发票"，维度不同（原表 P8 问题的答案）</t>
-        </is>
-      </c>
-      <c r="F8" s="141" t="inlineStr">
-        <is>
-          <t>① 开具地=开票方地址？税号国不一致时如何处理？② 认可 R7/R8 的边界划分吗？③ LGAP 附件发票需 OCR 提取，接受吗？置信度要求？</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="142" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="B9" s="142" t="inlineStr">
-        <is>
-          <t>无 PO/合同/汇款明细的付款</t>
-        </is>
-      </c>
-      <c r="C9" s="143" t="inlineStr">
-        <is>
-          <t>DT 已注"仅 LGAP、属正常场景"——那这条还告警吗</t>
-        </is>
-      </c>
-      <c r="D9" s="143" t="inlineStr">
-        <is>
-          <t>LGAP 付款申请记录（该场景仅存在于 LGAP）</t>
-        </is>
-      </c>
-      <c r="E9" s="143" t="inlineStr">
-        <is>
-          <t>不单独告警，仅作为付款的风险特征参与评分（无 PO = 少一道三单匹配防线）</t>
-        </is>
-      </c>
-      <c r="F9" s="143" t="inlineStr">
-        <is>
-          <t>确认：只记录不告警？还是特定费用类别之外的无 PO 付款仍要告警？</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="142" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="B10" s="142" t="inlineStr">
-        <is>
-          <t>资源与活动规模不相称</t>
-        </is>
-      </c>
-      <c r="C10" s="143" t="inlineStr">
-        <is>
-          <t>① 比例阈值
-② 历史窗口
-③ 海外无"注册资本"概念用什么替代</t>
-        </is>
-      </c>
-      <c r="D10" s="143" t="inlineStr">
-        <is>
-          <t>注册资本：天眼查（中国）/ DJ（海外，部分国家缺失）；历史 PO：Ariba；历史付款：S4 AP</t>
-        </is>
-      </c>
-      <c r="E10" s="143" t="inlineStr">
-        <is>
-          <t>建议：滚动 12 个月累计付款 &gt; 注册资本 × 10 触发（阈值可调）；海外缺注册资本时用员工数/营收区间替代或跳过</t>
-        </is>
-      </c>
-      <c r="F10" s="143" t="inlineStr">
-        <is>
-          <t>① 倍数阈值定多少？② 窗口 12 个月可以吗？③ 海外替代口径认可吗？</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="140" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="B11" s="140" t="inlineStr">
-        <is>
-          <t>A3 主营业务≠PO品类（准确率100%）</t>
-        </is>
-      </c>
-      <c r="C11" s="141" t="inlineStr">
-        <is>
-          <t>① "不相关"的判定标准
-② 品类粒度
-③ LLM 语义判定是否可接受</t>
-        </is>
-      </c>
-      <c r="D11" s="141" t="inlineStr">
-        <is>
-          <t>经营范围：天眼查/DJ；品类：Ariba commodity code（UNSPSC 树，可选大类或细类层级）</t>
-        </is>
-      </c>
-      <c r="E11" s="141" t="inlineStr">
-        <is>
-          <t>用 LLM 做语义相关性判定，低于阈值触发；品类先用大类层级（误报少）；判定结果附解释供复核</t>
-        </is>
-      </c>
-      <c r="F11" s="141" t="inlineStr">
-        <is>
-          <t>① 接受 LLM 判定吗？需要多高置信度？② 品类用大类还是细类？③ 贸易类公司（经营范围极宽）如何处理？</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="142" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="B12" s="142" t="inlineStr">
-        <is>
-          <t>对新供应商付款突增</t>
-        </is>
-      </c>
-      <c r="C12" s="143" t="inlineStr">
-        <is>
-          <t>① 500% 的基线是什么
-② 单笔还是累计
-③ "新"的起点</t>
-        </is>
-      </c>
-      <c r="D12" s="143" t="inlineStr">
-        <is>
-          <t>入库日期：S4 BP / Ariba SLP；付款流水：S4（全渠道含 LGAP）</t>
-        </is>
-      </c>
-      <c r="E12" s="143" t="inlineStr">
-        <is>
-          <t>新=入库 12 个月内（DT 注）；基线=该供应商此前 6 个月月均付款；月累计 &gt; 基线×5 触发；无历史（首单即大额）另设绝对阈值</t>
-        </is>
-      </c>
-      <c r="F12" s="143" t="inlineStr">
-        <is>
-          <t>① 基线口径认可吗？② 首单大额的绝对阈值定多少？③ 500% 是 DT 建议值，法务认可吗？</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="142" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="B13" s="142" t="inlineStr">
-        <is>
-          <t>周末/节假日交易</t>
-        </is>
-      </c>
-      <c r="C13" s="143" t="inlineStr">
-        <is>
-          <t>① 以哪个日期为准
-② 以哪国日历为准</t>
-        </is>
-      </c>
-      <c r="D13" s="143" t="inlineStr">
-        <is>
-          <t>候选日期：a.付款执行日（S4 清账日）b.发票日期 c.付款申请日（LGAP/Ariba）
-日历：付款方所在国（原表 O13 已倾向 payer side）</t>
-        </is>
-      </c>
-      <c r="E13" s="143" t="inlineStr">
-        <is>
-          <t>用【付款执行日】（实际资金动作；申请日/发票日会误报）；日历按付款方所在国</t>
-        </is>
-      </c>
-      <c r="F13" s="143" t="inlineStr">
-        <is>
-          <t>① 日期口径确认？② 付款方=联想付款主体所在国，还是收款方所在国？（原表写 payer 但值得再确认）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="142" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="B14" s="142" t="inlineStr">
-        <is>
-          <t>汇入无明显关联账户</t>
-        </is>
-      </c>
-      <c r="C14" s="143" t="inlineStr">
-        <is>
-          <t>① "明显关联"的定义
-② 此条是否保留（取决于 LGAP 系统管控）</t>
-        </is>
-      </c>
-      <c r="D14" s="143" t="inlineStr">
-        <is>
-          <t>登记账户：S4 供应商主数据的银行账户；实际收款账户：付款申请/凭证；关联判定：天眼查/DJ 股权关系</t>
-        </is>
-      </c>
-      <c r="E14" s="143" t="inlineStr">
-        <is>
-          <t>关联=同一实体或持股 ≥50% 的关联公司（原表 K14 自己提的问法）；若 DT 确认 LGAP 已硬管控则此条移除</t>
-        </is>
-      </c>
-      <c r="F14" s="143" t="inlineStr">
-        <is>
-          <t>① 关联阈值 50% 认可吗？集团财务公司代收算关联吗？② 等 DT 结论后决定去留</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="140" t="inlineStr">
-        <is>
-          <t>R15</t>
-        </is>
-      </c>
-      <c r="B15" s="140" t="inlineStr">
-        <is>
-          <t>A4 虚假发票（准确率100%）</t>
-        </is>
-      </c>
-      <c r="C15" s="141" t="inlineStr">
-        <is>
-          <t>① "虚假"的判定手段（中外不同）
-② 历史发票如何核验
-③ 发票影像可得性</t>
-        </is>
-      </c>
-      <c r="D15" s="141" t="inlineStr">
-        <is>
-          <t>中国：税局增值税发票查验平台；海外：发票号去重（S4 AP 历史）+ 模板/字段异常检测；影像：Ariba Network / LGAP 附件</t>
-        </is>
-      </c>
-      <c r="E15" s="141" t="inlineStr">
-        <is>
-          <t>中国走税局查验（硬判据）；海外先做重复号+连号+字段异常三项（软判据，命中转人工）</t>
-        </is>
-      </c>
-      <c r="F15" s="141" t="inlineStr">
-        <is>
-          <t>① 海外"虚假"以哪些特征为准？软判据也算 T1 吗？② 历史发票核验范围（回溯多久）？③ 查验不通过是否直接=欺诈结论？</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="144" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="B16" s="144" t="inlineStr">
-        <is>
-          <t>跨规则统一口径</t>
-        </is>
-      </c>
-      <c r="C16" s="145" t="inlineStr">
-        <is>
-          <t>① 金额阈值的币种折算
-② 国别字段优先级
-③ 复核时限的日历口径</t>
-        </is>
-      </c>
-      <c r="D16" s="145" t="inlineStr">
-        <is>
-          <t>多币种付款（S4 有交易币种与本位币）；多个国别字段可能互相矛盾</t>
-        </is>
-      </c>
-      <c r="E16" s="145" t="inlineStr">
-        <is>
-          <t>金额统一折算 USD（按付款日汇率）；国别矛盾时优先级：银行国 &gt; 发票国 &gt; 注册国（供讨论）；SLA 按自然日</t>
-        </is>
-      </c>
-      <c r="F16" s="145" t="inlineStr">
-        <is>
-          <t>① 币种口径？② 国别优先级？③ T1 的 24 小时按自然日还是工作日？</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/支付监控场景_中文版-0709-v2.xlsx
+++ b/docs/支付监控场景_中文版-0709-v2.xlsx
@@ -6633,7 +6633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.1640625" customWidth="1" style="63" min="1" max="1"/>
@@ -6652,6 +6652,8 @@
     <col width="41.6640625" customWidth="1" style="63" min="14" max="14"/>
     <col hidden="1" width="26.83203125" customWidth="1" style="63" min="16" max="16"/>
     <col width="22" customWidth="1" style="63" min="17" max="17"/>
+    <col width="52" customWidth="1" style="63" min="18" max="18"/>
+    <col width="42" customWidth="1" style="63" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="63">
@@ -6740,6 +6742,16 @@
           <t>Direction</t>
         </is>
       </c>
+      <c r="R1" s="74" t="inlineStr">
+        <is>
+          <t>Legal Confirmation · Proposed Basis</t>
+        </is>
+      </c>
+      <c r="S1" s="74" t="inlineStr">
+        <is>
+          <t>Legal Confirmation · To Decide</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="96" customHeight="1" s="63">
       <c r="B2" s="77" t="inlineStr">
@@ -6824,6 +6836,20 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="R2" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) which country fields (2) CPI threshold (3) list ownership
+Candidates: registration country (S4 BP) / place of business / invoice country (Ariba|LGAP) / bank country (SWIFT parse)
+Proposal: check all four; any hit triggers; CPI &lt;40 = high risk; list maintained yearly by Brenda</t>
+        </is>
+      </c>
+      <c r="S2" s="146" t="inlineStr">
+        <is>
+          <t>(1) All-four-countries approach OK, or only some?
+(2) CPI threshold?
+(3) List refresh cycle &amp; owner</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1" s="63">
       <c r="B3" s="77" t="inlineStr">
@@ -6906,6 +6932,18 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="R3" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) does the grey list trigger too (2) which sanctions regimes
+Proposal: black + grey both trigger (grey at lower priority); sanctions base = OFAC + EU + UN</t>
+        </is>
+      </c>
+      <c r="S3" s="146" t="inlineStr">
+        <is>
+          <t>(1) Treat grey list same as black?
+(2) Which 'economic sanctions laws' (open question in K3)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="64" customHeight="1" s="63">
       <c r="B4" s="77" t="inlineStr">
@@ -6981,6 +7019,20 @@
       <c r="Q4" s="138" t="inlineStr">
         <is>
           <t>Both</t>
+        </is>
+      </c>
+      <c r="R4" s="146" t="inlineStr">
+        <is>
+          <t>* MAJOR ambiguity: which route does 'routed through' mean
+Candidates: a. goods route (Ariba PO has only ship-from/to; full route needs logistics TMS - unavailable) b. funds route (receiving/intermediary bank country, S4/SWIFT - available)
+Proposal: start with the FUNDS route (closer to laundering substance); approximate goods route by PO endpoints; use the EU offshore financial centres list</t>
+        </is>
+      </c>
+      <c r="S4" s="146" t="inlineStr">
+        <is>
+          <t>(1) Funds route, goods route, or both?
+(2) Endpoints-only (no full route) acceptable?
+(3) Confirm the offshore list</t>
         </is>
       </c>
     </row>
@@ -7059,6 +7111,20 @@
       <c r="Q5" s="138" t="inlineStr">
         <is>
           <t>Both</t>
+        </is>
+      </c>
+      <c r="R5" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) proceeding types &amp; lookback (2) which parties (3) internal records
+Candidates: Tianyancha (CN) / DJ (ROW) litigation; internal corrupt-party payment history (S4 AP) - but no 'known corrupt party' list exists today
+Proposal: corruption/fraud/ML-related only, last 5 years; company + legal rep + controlling shareholder</t>
+        </is>
+      </c>
+      <c r="S5" s="146" t="inlineStr">
+        <is>
+          <t>(1) Proceeding types &amp; years?
+(2) Party scope?
+(3) Which team owns the internal 'known corrupt party' list?</t>
         </is>
       </c>
     </row>
@@ -7139,6 +7205,19 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="R6" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) ownership depth &amp; threshold (2) PEP source
+Candidates: Tianyancha equity (CN) / DJ (ROW); PEP db = DJ; role list per D6
+Proposal: 2 levels deep; &gt;=10% stake or any D6 role; high-risk-jurisdiction PEP weighted up at investigation</t>
+        </is>
+      </c>
+      <c r="S6" s="146" t="inlineStr">
+        <is>
+          <t>(1) Depth &amp; stake threshold?
+(2) Is DJ's PEP db enough for Chinese officials?</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1" s="63">
       <c r="A7" s="89" t="inlineStr">
@@ -7221,6 +7300,19 @@
           <t>Both — currently payables only</t>
         </is>
       </c>
+      <c r="R7" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: 'principal place of business' = registration country or actual?
+Candidates: a. registration country (S4 BP, internal) b. actual place of business (TYC/DJ, external)
+Proposal: detection uses registration country (automatable); actual place verified at investigation; bank country parsed from receiving-account SWIFT prefix (S4)</t>
+        </is>
+      </c>
+      <c r="S7" s="146" t="inlineStr">
+        <is>
+          <t>(1) Registration country acceptable as the basis? Which wins on conflict?
+(2) Judge per account when a vendor has several receiving accounts?</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1" s="63">
       <c r="A8" s="89" t="inlineStr">
@@ -7306,6 +7398,20 @@
       <c r="Q8" s="138" t="inlineStr">
         <is>
           <t>Payables (vendor)</t>
+        </is>
+      </c>
+      <c r="R8" s="146" t="inlineStr">
+        <is>
+          <t>* 'Invoice origin' = which field on the invoice
+Candidates: a. issuer address country b. remit-to country c. tax-ID country (VAT prefix); payer country = Lenovo company-code country (S4)
+Proposal: issuer address country as primary, tax-ID country as cross-check; boundary vs row 7: R7 = bank vs vendor, R8 = payer entity vs invoice (answers P8)</t>
+        </is>
+      </c>
+      <c r="S8" s="146" t="inlineStr">
+        <is>
+          <t>(1) Origin = issuer address? What if tax-ID country differs?
+(2) Agree with the R7/R8 boundary?
+(3) LGAP attachment invoices need OCR - acceptable? Confidence bar?</t>
         </is>
       </c>
     </row>
@@ -7371,6 +7477,17 @@
       <c r="Q9" s="138" t="inlineStr">
         <is>
           <t>Payables (vendor)</t>
+        </is>
+      </c>
+      <c r="R9" s="146" t="inlineStr">
+        <is>
+          <t>DT noted 'LGAP only, normal scenario'
+Proposal: no standalone alert; use as a risk feature in scoring only (no PO = one less 3-way-match defence)</t>
+        </is>
+      </c>
+      <c r="S9" s="146" t="inlineStr">
+        <is>
+          <t>Confirm: record-only? Or should non-PO payments outside specific expense types still alert?</t>
         </is>
       </c>
     </row>
@@ -7447,6 +7564,20 @@
           <t>Payables (vendor)</t>
         </is>
       </c>
+      <c r="R10" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) multiple threshold (2) window (3) no registered-capital concept abroad
+Candidates: registered capital = TYC/DJ (missing in some countries); PO history = Ariba; payments = S4 AP
+Proposal: rolling 12-month payments &gt; registered capital x10 triggers; abroad use headcount/revenue band or skip</t>
+        </is>
+      </c>
+      <c r="S10" s="146" t="inlineStr">
+        <is>
+          <t>(1) Multiple threshold?
+(2) 12-month window OK?
+(3) Overseas fallback acceptable?</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="72" customHeight="1" s="63">
       <c r="A11" s="89" t="inlineStr">
@@ -7524,6 +7655,20 @@
       <c r="Q11" s="138" t="inlineStr">
         <is>
           <t>Payables (vendor)</t>
+        </is>
+      </c>
+      <c r="R11" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) 'irrelevant' criterion (2) category granularity (3) LLM judgment acceptable?
+Candidates: business scope = TYC/DJ; category = Ariba commodity code (UNSPSC tree)
+Proposal: LLM semantic-relevance scoring with written rationale; start at top-level categories (fewer false positives)</t>
+        </is>
+      </c>
+      <c r="S11" s="146" t="inlineStr">
+        <is>
+          <t>(1) Accept LLM judgment? Confidence bar?
+(2) Top-level or detailed categories?
+(3) How to treat trading companies (very broad scope)?</t>
         </is>
       </c>
     </row>
@@ -7597,6 +7742,20 @@
           <t>Payables (vendor)</t>
         </is>
       </c>
+      <c r="R12" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) baseline (2) per-payment or cumulative (3) first-order-large case
+Candidates: onboarding date = S4 BP / Ariba SLP; payment history = S4 (incl. LGAP channel)
+Proposal: new = onboarded &lt;12 months; baseline = prior 6-month monthly average; monthly total &gt; baseline x5 triggers; separate absolute threshold for large first orders</t>
+        </is>
+      </c>
+      <c r="S12" s="146" t="inlineStr">
+        <is>
+          <t>(1) Baseline OK?
+(2) Absolute threshold for large first orders?
+(3) 500% (DT's suggestion) - does Legal agree?</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1" s="63">
       <c r="B13" s="77" t="inlineStr">
@@ -7668,6 +7827,19 @@
           <t>Payables (vendor)</t>
         </is>
       </c>
+      <c r="R13" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) which date (2) whose calendar
+Candidates: a. payment execution date (S4 clearing) b. invoice date c. request date (LGAP/Ariba)
+Proposal: use payment execution date (actual money movement; request/invoice dates over-alert); calendar of the payer country (O13 already leans payer side)</t>
+        </is>
+      </c>
+      <c r="S13" s="146" t="inlineStr">
+        <is>
+          <t>(1) Confirm the date basis?
+(2) Payer = Lenovo paying entity's country - confirm?</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="108" customHeight="1" s="63">
       <c r="B14" s="77" t="inlineStr">
@@ -7737,6 +7909,19 @@
           <t>Payables (vendor)</t>
         </is>
       </c>
+      <c r="R14" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) definition of 'apparent connection' (2) keep or drop
+Candidates: registered account = S4 vendor master; actual receiving account = payment request/document; connection via TYC/DJ equity
+Proposal: connection = same entity or &gt;=50%-owned affiliate (K14's own suggestion); drop if DT confirms LGAP hard control</t>
+        </is>
+      </c>
+      <c r="S14" s="146" t="inlineStr">
+        <is>
+          <t>(1) 50% threshold OK? Does group treasury collection count as connected?
+(2) Decide after DT's finding</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="54" customHeight="1" s="63">
       <c r="A15" s="89" t="inlineStr">
@@ -7805,6 +7990,20 @@
       <c r="Q15" s="138" t="inlineStr">
         <is>
           <t>Payables (vendor)</t>
+        </is>
+      </c>
+      <c r="R15" s="146" t="inlineStr">
+        <is>
+          <t>To confirm: (1) 'fake' criteria (CN vs ROW) (2) historical invoice checks (3) image availability
+Candidates: CN = tax-bureau verification platform (hard evidence); ROW = duplicate numbers (S4 AP) + sequential numbers + template/field anomalies (soft); images = Ariba Network / LGAP attachments
+Proposal: CN via tax verification; ROW: 3 soft checks route to manual review</t>
+        </is>
+      </c>
+      <c r="S15" s="146" t="inlineStr">
+        <is>
+          <t>(1) Do ROW soft checks still count as T1?
+(2) How far back for historical invoices?
+(3) Failed verification = fraud verdict directly?</t>
         </is>
       </c>
     </row>
@@ -7942,6 +8141,26 @@
       <c r="Q21" s="138" t="inlineStr">
         <is>
           <t>Payables (vendor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="147" t="inlineStr">
+        <is>
+          <t>Cross-rule</t>
+        </is>
+      </c>
+      <c r="R23" s="146" t="inlineStr">
+        <is>
+          <t>Cross-rule conventions
+Proposal: amounts converted to USD (payment-date FX); country-field precedence bank &gt; invoice &gt; registration (for discussion); SLA in calendar days</t>
+        </is>
+      </c>
+      <c r="S23" s="146" t="inlineStr">
+        <is>
+          <t>(1) Currency conversion basis?
+(2) Country-field precedence?
+(3) T1's 24h: calendar or business days?</t>
         </is>
       </c>
     </row>

--- a/docs/支付监控场景_中文版-0709-v2.xlsx
+++ b/docs/支付监控场景_中文版-0709-v2.xlsx
@@ -5106,7 +5106,7 @@
       </c>
       <c r="R2" s="146" t="inlineStr">
         <is>
-          <t>待确认：①国别口径 ②CPI 阈值 ③名单维护
+          <t>🟡 待确认：①国别口径 ②CPI 阈值 ③名单维护
 候选：注册国(S4 BP)/营业地/发票国(Ariba|LGAP)/银行国(SWIFT解析)
 建议：四国别都查，任一命中即触发；CPI &lt;40 算高风险；名单 Brenda 年度更新</t>
         </is>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="R3" s="146" t="inlineStr">
         <is>
-          <t>待确认：①灰名单是否同级触发 ②制裁体系范围
+          <t>🟢 待确认：①灰名单是否同级触发 ②制裁体系范围
 建议：黑+灰名单都触发（灰名单优先级略低）；制裁体系以 OFAC+EU+UN 为基础</t>
         </is>
       </c>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="R4" s="146" t="inlineStr">
         <is>
-          <t>★重大歧义："中转"查什么路径
+          <t>🔴 ★重大歧义："中转"查什么路径
 候选：a.货物路径（Ariba PO 仅有起运/目的地，完整路径需物流TMS，暂无）b.资金路径（收款行/中转行国别，S4/SWIFT，数据可得）
 建议：先做资金路径（更贴洗钱本质）；货物路径用 PO 起终点近似；名单用 EU 离岸金融中心清单</t>
         </is>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="R5" s="146" t="inlineStr">
         <is>
-          <t>待确认：①诉讼类型与时间窗 ②主体范围 ③内部记录
+          <t>🟢 待确认：①诉讼类型与时间窗 ②主体范围 ③内部记录
 候选：天眼查(中国)/DJ(海外)诉讼库；内部腐败方付款记录（S4 AP 历史，但"已知腐败方"名单目前不存在）
 建议：仅腐败/欺诈/洗钱相关，近 5 年；查公司+法代+控股股东</t>
         </is>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="R6" s="146" t="inlineStr">
         <is>
-          <t>待确认：①穿透层数与持股阈值 ②PEP 库来源
+          <t>🟢 待确认：①穿透层数与持股阈值 ②PEP 库来源
 候选：天眼查股权(中国)/DJ(海外)；PEP 库=DJ；角色清单见 D6
 建议：穿透 2 层；持股≥10% 或任 D6 所列职务即查；高风险辖区 PEP 调查阶段加重</t>
         </is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="R7" s="146" t="inlineStr">
         <is>
-          <t>待确认："主要经营地"=注册国还是实际经营地
+          <t>🟢 待确认："主要经营地"=注册国还是实际经营地
 候选：a.注册国（S4 BP，内部可得）b.实际经营地（天眼查/DJ）
 建议：检测阶段用注册国（可自动化）；实际经营地留调查阶段；银行属地以收款账户 SWIFT 前缀解析（S4）</t>
         </is>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="R8" s="146" t="inlineStr">
         <is>
-          <t>★"发票开具地"=发票上哪个字段
+          <t>🔴 ★"发票开具地"=发票上哪个字段
 候选：a.开票方地址国 b.remit-to 汇款地址国 c.税号归属国（VAT 前缀）；付款方国=联想 company code 所属国（S4）
 建议：以开票方地址国为主判据，税号国交叉校验；与 R7 边界：R7 查银行vs供应商，R8 查付款主体vs发票（P8 问题的答案）</t>
         </is>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="R9" s="146" t="inlineStr">
         <is>
-          <t>DT 已注"仅 LGAP、正常场景"
+          <t>🔴 DT 已注"仅 LGAP、正常场景"
 建议：不单独告警，仅作为风险特征参与评分（无 PO=少一道三单匹配防线）</t>
         </is>
       </c>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="R10" s="146" t="inlineStr">
         <is>
-          <t>待确认：①倍数阈值 ②窗口 ③海外无注册资本概念
+          <t>🟡 待确认：①倍数阈值 ②窗口 ③海外无注册资本概念
 候选：注册资本=天眼查/DJ（海外部分国家缺失）；历史 PO=Ariba；付款=S4 AP
 建议：滚动 12 个月累计付款 &gt; 注册资本×10 触发；海外缺失时用员工数/营收区间替代或跳过</t>
         </is>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="R11" s="146" t="inlineStr">
         <is>
-          <t>待确认：①"不相关"判定标准 ②品类粒度 ③LLM 判定可否
+          <t>🟢 待确认：①"不相关"判定标准 ②品类粒度 ③LLM 判定可否
 候选：经营范围=天眼查/DJ；品类=Ariba commodity code（UNSPSC 树）
 建议：LLM 语义相关性判定+附解释；品类先用大类层级（误报少）</t>
         </is>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="R12" s="146" t="inlineStr">
         <is>
-          <t>待确认：①基线口径 ②单笔还是累计 ③首单大额
+          <t>🟡 待确认：①基线口径 ②单笔还是累计 ③首单大额
 候选：入库日期=S4 BP/Ariba SLP；流水=S4（含 LGAP 通道）
 建议：新=入库 12 个月内；基线=此前 6 个月月均；月累计&gt;基线×5 触发；首单即大额另设绝对阈值</t>
         </is>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="R13" s="146" t="inlineStr">
         <is>
-          <t>待确认：①以哪个日期为准 ②哪国日历
+          <t>🟢 待确认：①以哪个日期为准 ②哪国日历
 候选：a.付款执行日（S4 清账日）b.发票日期 c.申请日（LGAP/Ariba）
 建议：用付款执行日（实际资金动作，申请日/发票日会误报）；日历按付款方所在国（O13 已倾向 payer side）</t>
         </is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="R14" s="146" t="inlineStr">
         <is>
-          <t>待确认：①"明显关联"定义 ②此条去留
+          <t>🟢 待确认：①"明显关联"定义 ②此条去留
 候选：登记账户=S4 供应商主数据；实际收款账户=付款申请/凭证；关联判定=天眼查/DJ 股权
 建议：关联=同一实体或持股≥50% 关联公司（K14 自提问法）；若 DT 确认 LGAP 已硬管控则移除</t>
         </is>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="R15" s="146" t="inlineStr">
         <is>
-          <t>待确认：①中外"虚假"判定手段 ②历史发票核验 ③影像可得性
+          <t>🔴 待确认：①中外"虚假"判定手段 ②历史发票核验 ③影像可得性
 候选：中国=税局查验平台（硬判据）；海外=发票号去重（S4 AP）+连号+模板/字段异常（软判据）；影像=Ariba Network/LGAP 附件
 建议：中国走税局查验；海外三项软判据命中转人工</t>
         </is>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="R23" s="146" t="inlineStr">
         <is>
-          <t>跨规则通用口径
+          <t>🟡 跨规则通用口径
 建议：金额统一折算 USD（按付款日汇率）；国别矛盾时优先级 银行国&gt;发票国&gt;注册国（供讨论）；SLA 按自然日</t>
         </is>
       </c>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="R2" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) which country fields (2) CPI threshold (3) list ownership
+          <t>🟡 To confirm: (1) which country fields (2) CPI threshold (3) list ownership
 Candidates: registration country (S4 BP) / place of business / invoice country (Ariba|LGAP) / bank country (SWIFT parse)
 Proposal: check all four; any hit triggers; CPI &lt;40 = high risk; list maintained yearly by Brenda</t>
         </is>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="R3" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) does the grey list trigger too (2) which sanctions regimes
+          <t>🟢 To confirm: (1) does the grey list trigger too (2) which sanctions regimes
 Proposal: black + grey both trigger (grey at lower priority); sanctions base = OFAC + EU + UN</t>
         </is>
       </c>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="R4" s="146" t="inlineStr">
         <is>
-          <t>* MAJOR ambiguity: which route does 'routed through' mean
+          <t>🔴 * MAJOR ambiguity: which route does 'routed through' mean
 Candidates: a. goods route (Ariba PO has only ship-from/to; full route needs logistics TMS - unavailable) b. funds route (receiving/intermediary bank country, S4/SWIFT - available)
 Proposal: start with the FUNDS route (closer to laundering substance); approximate goods route by PO endpoints; use the EU offshore financial centres list</t>
         </is>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="R5" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) proceeding types &amp; lookback (2) which parties (3) internal records
+          <t>🟢 To confirm: (1) proceeding types &amp; lookback (2) which parties (3) internal records
 Candidates: Tianyancha (CN) / DJ (ROW) litigation; internal corrupt-party payment history (S4 AP) - but no 'known corrupt party' list exists today
 Proposal: corruption/fraud/ML-related only, last 5 years; company + legal rep + controlling shareholder</t>
         </is>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="R6" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) ownership depth &amp; threshold (2) PEP source
+          <t>🟢 To confirm: (1) ownership depth &amp; threshold (2) PEP source
 Candidates: Tianyancha equity (CN) / DJ (ROW); PEP db = DJ; role list per D6
 Proposal: 2 levels deep; &gt;=10% stake or any D6 role; high-risk-jurisdiction PEP weighted up at investigation</t>
         </is>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="R7" s="146" t="inlineStr">
         <is>
-          <t>To confirm: 'principal place of business' = registration country or actual?
+          <t>🟢 To confirm: 'principal place of business' = registration country or actual?
 Candidates: a. registration country (S4 BP, internal) b. actual place of business (TYC/DJ, external)
 Proposal: detection uses registration country (automatable); actual place verified at investigation; bank country parsed from receiving-account SWIFT prefix (S4)</t>
         </is>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="R8" s="146" t="inlineStr">
         <is>
-          <t>* 'Invoice origin' = which field on the invoice
+          <t>🔴 * 'Invoice origin' = which field on the invoice
 Candidates: a. issuer address country b. remit-to country c. tax-ID country (VAT prefix); payer country = Lenovo company-code country (S4)
 Proposal: issuer address country as primary, tax-ID country as cross-check; boundary vs row 7: R7 = bank vs vendor, R8 = payer entity vs invoice (answers P8)</t>
         </is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="R9" s="146" t="inlineStr">
         <is>
-          <t>DT noted 'LGAP only, normal scenario'
+          <t>🔴 DT noted 'LGAP only, normal scenario'
 Proposal: no standalone alert; use as a risk feature in scoring only (no PO = one less 3-way-match defence)</t>
         </is>
       </c>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="R10" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) multiple threshold (2) window (3) no registered-capital concept abroad
+          <t>🟡 To confirm: (1) multiple threshold (2) window (3) no registered-capital concept abroad
 Candidates: registered capital = TYC/DJ (missing in some countries); PO history = Ariba; payments = S4 AP
 Proposal: rolling 12-month payments &gt; registered capital x10 triggers; abroad use headcount/revenue band or skip</t>
         </is>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="R11" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) 'irrelevant' criterion (2) category granularity (3) LLM judgment acceptable?
+          <t>🟢 To confirm: (1) 'irrelevant' criterion (2) category granularity (3) LLM judgment acceptable?
 Candidates: business scope = TYC/DJ; category = Ariba commodity code (UNSPSC tree)
 Proposal: LLM semantic-relevance scoring with written rationale; start at top-level categories (fewer false positives)</t>
         </is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="R12" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) baseline (2) per-payment or cumulative (3) first-order-large case
+          <t>🟡 To confirm: (1) baseline (2) per-payment or cumulative (3) first-order-large case
 Candidates: onboarding date = S4 BP / Ariba SLP; payment history = S4 (incl. LGAP channel)
 Proposal: new = onboarded &lt;12 months; baseline = prior 6-month monthly average; monthly total &gt; baseline x5 triggers; separate absolute threshold for large first orders</t>
         </is>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="R13" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) which date (2) whose calendar
+          <t>🟢 To confirm: (1) which date (2) whose calendar
 Candidates: a. payment execution date (S4 clearing) b. invoice date c. request date (LGAP/Ariba)
 Proposal: use payment execution date (actual money movement; request/invoice dates over-alert); calendar of the payer country (O13 already leans payer side)</t>
         </is>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="R14" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) definition of 'apparent connection' (2) keep or drop
+          <t>🟢 To confirm: (1) definition of 'apparent connection' (2) keep or drop
 Candidates: registered account = S4 vendor master; actual receiving account = payment request/document; connection via TYC/DJ equity
 Proposal: connection = same entity or &gt;=50%-owned affiliate (K14's own suggestion); drop if DT confirms LGAP hard control</t>
         </is>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="R15" s="146" t="inlineStr">
         <is>
-          <t>To confirm: (1) 'fake' criteria (CN vs ROW) (2) historical invoice checks (3) image availability
+          <t>🔴 To confirm: (1) 'fake' criteria (CN vs ROW) (2) historical invoice checks (3) image availability
 Candidates: CN = tax-bureau verification platform (hard evidence); ROW = duplicate numbers (S4 AP) + sequential numbers + template/field anomalies (soft); images = Ariba Network / LGAP attachments
 Proposal: CN via tax verification; ROW: 3 soft checks route to manual review</t>
         </is>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="R23" s="146" t="inlineStr">
         <is>
-          <t>Cross-rule conventions
+          <t>🟡 Cross-rule conventions
 Proposal: amounts converted to USD (payment-date FX); country-field precedence bank &gt; invoice &gt; registration (for discussion); SLA in calendar days</t>
         </is>
       </c>
